--- a/VerveStacks_AUS/SysSettings.xlsx
+++ b/VerveStacks_AUS/SysSettings.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9870CC7C-C54D-4601-B5B4-6F1A113ED86A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A59C32A9-14D1-40E0-B69B-2D7CBC55FFDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="221">
   <si>
     <t>~BookRegions_Map</t>
   </si>
@@ -100,12 +100,6 @@
     <t>bioenergy</t>
   </si>
   <si>
-    <t>gas</t>
-  </si>
-  <si>
-    <t>coal</t>
-  </si>
-  <si>
     <t>hydrogen</t>
   </si>
   <si>
@@ -121,12 +115,6 @@
     <t>solar</t>
   </si>
   <si>
-    <t>wind</t>
-  </si>
-  <si>
-    <t>oil</t>
-  </si>
-  <si>
     <t>ELC</t>
   </si>
   <si>
@@ -658,28 +646,61 @@
     <t>co2net</t>
   </si>
   <si>
+    <t>flo_mark</t>
+  </si>
+  <si>
+    <t>hydrogen_allsect</t>
+  </si>
+  <si>
+    <t>Hydrogen demand - all sectors</t>
+  </si>
+  <si>
+    <t>windon</t>
+  </si>
+  <si>
+    <t>windoff</t>
+  </si>
+  <si>
+    <t>wind onshore</t>
+  </si>
+  <si>
+    <t>wind offshore</t>
+  </si>
+  <si>
+    <t>COAL</t>
+  </si>
+  <si>
+    <t>GAS</t>
+  </si>
+  <si>
+    <t>OIL</t>
+  </si>
+  <si>
     <t>AUS</t>
   </si>
   <si>
-    <t>Unit</t>
-  </si>
-  <si>
-    <t>ELC_Sol-AUS</t>
-  </si>
-  <si>
-    <t>DAYNITE</t>
+    <t>set</t>
+  </si>
+  <si>
+    <t>elc_spv-AUS</t>
+  </si>
+  <si>
+    <t>solar electricity generation</t>
   </si>
   <si>
     <t>TWh</t>
   </si>
   <si>
-    <t>Solar electricity produced in - Australia</t>
-  </si>
-  <si>
-    <t>ELC_Win-AUS</t>
-  </si>
-  <si>
-    <t>Wind electricity produced in - Australia</t>
+    <t>elc_wof-AUS</t>
+  </si>
+  <si>
+    <t>offshore wind electricity generation</t>
+  </si>
+  <si>
+    <t>elc_won-AUS</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation</t>
   </si>
 </sst>
 </file>
@@ -703,7 +724,7 @@
     <numFmt numFmtId="175" formatCode="#,##0.0;\-#,##0.0;&quot;-&quot;"/>
     <numFmt numFmtId="176" formatCode="\Te\x\t"/>
   </numFmts>
-  <fonts count="57">
+  <fonts count="59">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1064,6 +1085,20 @@
       <color indexed="8"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="47">
@@ -1588,7 +1623,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="435">
+  <cellStyleXfs count="437">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -2136,8 +2171,10 @@
     <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="57" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3"/>
     <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="3" applyNumberFormat="1"/>
@@ -2161,8 +2198,10 @@
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="431" applyFont="1"/>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="234"/>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="234" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="435">
+  <cellStyles count="437">
     <cellStyle name="20% - Accent1 2" xfId="4" xr:uid="{822ECCD2-03B4-4EB0-AADE-6DECEB39BB19}"/>
     <cellStyle name="20% - Accent1 3" xfId="5" xr:uid="{58CA3325-8B37-45C5-A177-73E6AEE43B64}"/>
     <cellStyle name="20% - Accent2 2" xfId="6" xr:uid="{3C5AA3C1-DAA0-472F-BECC-C64D10D55099}"/>
@@ -2375,6 +2414,7 @@
     <cellStyle name="Monétaire [0]_03tabmat" xfId="208" xr:uid="{F0DE3656-7A58-4CA3-A5EE-8576552EC653}"/>
     <cellStyle name="Monétaire_03tabmat" xfId="209" xr:uid="{E08D72EA-6991-424D-A48D-6801B506315C}"/>
     <cellStyle name="Neutral 2" xfId="211" xr:uid="{0BD2AEA9-BAC5-48AA-B1A7-8F95AAE6853E}"/>
+    <cellStyle name="Neutral 2 2" xfId="435" xr:uid="{773FC3D2-CB25-40C1-9022-B7616488FC25}"/>
     <cellStyle name="Neutral 3" xfId="210" xr:uid="{2435363D-5388-4D62-AE78-289118217843}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 10" xfId="212" xr:uid="{347F5622-C417-4F2E-B072-ECA7EBFFEE51}"/>
@@ -2474,6 +2514,7 @@
     <cellStyle name="Normal 3 5" xfId="306" xr:uid="{6443DAD9-14AD-440B-897A-2E9A24F0DF1D}"/>
     <cellStyle name="Normal 3 6" xfId="307" xr:uid="{E81CCC51-42D9-4E87-8496-29697C117EDE}"/>
     <cellStyle name="Normal 3 7" xfId="308" xr:uid="{5928F6C9-137F-431B-BF0D-7549BEA7EBFE}"/>
+    <cellStyle name="Normal 3 8" xfId="436" xr:uid="{552B16F0-55E2-4A8F-AA64-ACE13CE218AC}"/>
     <cellStyle name="Normal 30" xfId="309" xr:uid="{55B4AFDB-2E32-4F94-ABBB-FD32410C9D32}"/>
     <cellStyle name="Normal 31" xfId="310" xr:uid="{221EABEA-5450-4B12-B481-461C2BAE31B9}"/>
     <cellStyle name="Normal 32" xfId="311" xr:uid="{99908D0B-751D-4CA3-A3C2-C2D00549AE1A}"/>
@@ -3050,21 +3091,21 @@
         <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="F4" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="H4" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="2:8">
       <c r="F5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="H5" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -3075,7 +3116,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2F298A9-BCD9-4ABF-BE3B-9D1BDD3E7001}">
-  <dimension ref="B3:Q22"/>
+  <dimension ref="B3:R24"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="11.19921875" bestFit="1" customWidth="1"/>
@@ -3088,7 +3129,7 @@
     <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:17" ht="17.649999999999999" thickBot="1">
+    <row r="3" spans="2:18" ht="17.649999999999999" thickBot="1">
       <c r="B3" s="3" t="s">
         <v>8</v>
       </c>
@@ -3107,7 +3148,7 @@
       <c r="P3" s="2"/>
       <c r="Q3" s="2"/>
     </row>
-    <row r="4" spans="2:17" ht="15" thickTop="1" thickBot="1">
+    <row r="4" spans="2:18" ht="15" thickTop="1" thickBot="1">
       <c r="B4" s="5" t="s">
         <v>9</v>
       </c>
@@ -3133,22 +3174,25 @@
         <v>16</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>9</v>
+        <v>213</v>
       </c>
       <c r="N4" s="5" t="s">
         <v>10</v>
       </c>
       <c r="O4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="P4" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="P4" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="Q4" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="2:17">
+      <c r="R4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="2:18">
       <c r="B5" t="s">
         <v>17</v>
       </c>
@@ -3162,21 +3206,27 @@
         <v>17</v>
       </c>
       <c r="N5" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="O5" t="s">
+        <v>215</v>
+      </c>
+      <c r="P5" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>35</v>
+      </c>
+      <c r="R5" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="6" spans="2:18">
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="s">
         <v>209</v>
-      </c>
-      <c r="P5" t="s">
-        <v>210</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="6" spans="2:17">
-      <c r="C6" t="s">
-        <v>21</v>
       </c>
       <c r="E6" t="s">
         <v>18</v>
@@ -3185,125 +3235,176 @@
         <v>17</v>
       </c>
       <c r="N6" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="O6" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="P6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>35</v>
+      </c>
+      <c r="R6" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="7" spans="2:18">
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" t="s">
         <v>210</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="7" spans="2:17">
-      <c r="C7" t="s">
-        <v>20</v>
       </c>
       <c r="E7" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="8" spans="2:17">
+      <c r="M7" t="s">
+        <v>17</v>
+      </c>
+      <c r="N7" t="s">
+        <v>219</v>
+      </c>
+      <c r="O7" t="s">
+        <v>220</v>
+      </c>
+      <c r="P7" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>35</v>
+      </c>
+      <c r="R7" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="8" spans="2:18">
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E8" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="2:17">
+    <row r="9" spans="2:18">
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E9" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="2:17">
+    <row r="10" spans="2:18">
+      <c r="B10" t="s">
+        <v>17</v>
+      </c>
       <c r="C10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E10" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="2:17">
+    <row r="11" spans="2:18">
+      <c r="B11" t="s">
+        <v>17</v>
+      </c>
       <c r="C11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E11" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="2:17">
+    <row r="12" spans="2:18">
+      <c r="B12" t="s">
+        <v>17</v>
+      </c>
       <c r="C12" t="s">
-        <v>28</v>
+        <v>211</v>
       </c>
       <c r="E12" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="2:17">
+    <row r="13" spans="2:18">
+      <c r="B13" t="s">
+        <v>17</v>
+      </c>
       <c r="C13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E13" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="2:17">
+    <row r="14" spans="2:18">
+      <c r="B14" t="s">
+        <v>17</v>
+      </c>
       <c r="C14" t="s">
-        <v>27</v>
+        <v>205</v>
+      </c>
+      <c r="D14" t="s">
+        <v>207</v>
       </c>
       <c r="E14" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="2:17">
+    <row r="15" spans="2:18">
+      <c r="B15" t="s">
+        <v>17</v>
+      </c>
       <c r="C15" t="s">
-        <v>29</v>
+        <v>206</v>
       </c>
       <c r="D15" t="s">
-        <v>34</v>
+        <v>208</v>
       </c>
       <c r="E15" t="s">
         <v>18</v>
       </c>
-      <c r="F15" t="s">
-        <v>39</v>
-      </c>
-      <c r="G15" t="s">
-        <v>29</v>
-      </c>
-      <c r="I15" t="s">
+    </row>
+    <row r="16" spans="2:18">
+      <c r="B16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" t="s">
+        <v>25</v>
+      </c>
+      <c r="D16" t="s">
         <v>30</v>
-      </c>
-    </row>
-    <row r="16" spans="2:17">
-      <c r="B16" t="s">
-        <v>38</v>
-      </c>
-      <c r="C16" t="s">
-        <v>31</v>
-      </c>
-      <c r="D16" t="s">
-        <v>35</v>
       </c>
       <c r="E16" t="s">
         <v>18</v>
       </c>
+      <c r="F16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G16" t="s">
+        <v>25</v>
+      </c>
+      <c r="I16" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="17" spans="2:7">
       <c r="B17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C17" t="s">
-        <v>32</v>
+        <v>203</v>
       </c>
       <c r="D17" t="s">
-        <v>36</v>
+        <v>204</v>
       </c>
       <c r="E17" t="s">
         <v>18</v>
@@ -3311,13 +3412,13 @@
     </row>
     <row r="18" spans="2:7">
       <c r="B18" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C18" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D18" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E18" t="s">
         <v>18</v>
@@ -3325,57 +3426,91 @@
     </row>
     <row r="19" spans="2:7">
       <c r="B19" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="C19" t="s">
-        <v>201</v>
+        <v>28</v>
       </c>
       <c r="D19" t="s">
-        <v>202</v>
+        <v>32</v>
       </c>
       <c r="E19" t="s">
         <v>18</v>
       </c>
-      <c r="F19" t="s">
-        <v>39</v>
-      </c>
-      <c r="G19" t="s">
-        <v>29</v>
-      </c>
     </row>
     <row r="20" spans="2:7">
       <c r="B20" t="s">
+        <v>34</v>
+      </c>
+      <c r="C20" t="s">
+        <v>29</v>
+      </c>
+      <c r="D20" t="s">
+        <v>33</v>
+      </c>
+      <c r="E20" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7">
+      <c r="B21" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" t="s">
         <v>197</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D21" t="s">
         <v>198</v>
       </c>
-      <c r="D20" t="s">
-        <v>199</v>
-      </c>
-      <c r="E20" t="s">
+      <c r="E21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F21" t="s">
+        <v>35</v>
+      </c>
+      <c r="G21" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7">
+      <c r="B22" t="s">
+        <v>193</v>
+      </c>
+      <c r="C22" t="s">
+        <v>194</v>
+      </c>
+      <c r="D22" t="s">
+        <v>195</v>
+      </c>
+      <c r="E22" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7">
+      <c r="B23" t="s">
+        <v>193</v>
+      </c>
+      <c r="C23" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="21" spans="2:7">
-      <c r="C21" t="s">
-        <v>204</v>
-      </c>
-      <c r="E21" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="22" spans="2:7">
-      <c r="C22" t="s">
-        <v>205</v>
-      </c>
-      <c r="E22" t="s">
-        <v>200</v>
+      <c r="E23" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7">
+      <c r="B24" t="s">
+        <v>193</v>
+      </c>
+      <c r="C24" t="s">
+        <v>201</v>
+      </c>
+      <c r="E24" t="s">
+        <v>196</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C8:C332">
-    <sortCondition ref="C17:C332"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C8:C334">
+    <sortCondition ref="C19:C334"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3397,7 +3532,7 @@
   <sheetData>
     <row r="3" spans="2:7">
       <c r="B3" s="6" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="2:7">
@@ -3407,28 +3542,28 @@
     </row>
     <row r="7" spans="2:7">
       <c r="B7" s="6" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="2:7">
       <c r="B8" s="6" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="2:7">
       <c r="B11" s="6" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" spans="2:7" ht="14.25">
       <c r="B12" s="7" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E12" s="8" t="str">
         <f>"msy"&amp;COUNT(E14:E46)&amp;"_"&amp;MAX(E14:E46)</f>
@@ -3448,7 +3583,7 @@
         <v>1</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14" spans="2:7" ht="14.25">
@@ -3456,7 +3591,7 @@
         <v>5</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E14" s="6">
         <f t="shared" ref="E14:G14" si="1">$B$4</f>
@@ -3476,7 +3611,7 @@
         <v>5</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E15" s="6">
         <f>E14+3</f>
@@ -3496,7 +3631,7 @@
         <v>10</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E16" s="6">
         <f>E15+5</f>
@@ -3516,7 +3651,7 @@
         <v>10</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E17" s="6">
         <f t="shared" ref="E17:E20" si="2">E16+5</f>
@@ -3536,7 +3671,7 @@
         <v>10</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E18" s="6">
         <f t="shared" si="2"/>
@@ -3556,7 +3691,7 @@
         <v>10</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E19" s="6">
         <f t="shared" si="2"/>
@@ -3572,7 +3707,7 @@
         <v>10</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E20" s="6">
         <f t="shared" si="2"/>
@@ -3584,7 +3719,7 @@
         <v>10</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="2:7" ht="14.25">
@@ -3592,7 +3727,7 @@
         <v>10</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23" spans="2:7" ht="14.25">
@@ -3600,7 +3735,7 @@
         <v>10</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="24" spans="2:7" ht="14.25">
@@ -3608,37 +3743,37 @@
         <v>10</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="2:7" ht="14.25">
       <c r="B25" s="9"/>
       <c r="D25" s="6" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26" spans="2:7" ht="14.25">
       <c r="B26" s="9"/>
       <c r="D26" s="6" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="27" spans="2:7" ht="14.25">
       <c r="B27" s="9"/>
       <c r="D27" s="6" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28" spans="2:7" ht="14.25">
       <c r="B28" s="9"/>
       <c r="D28" s="6" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="29" spans="2:7" ht="14.25">
       <c r="B29" s="9"/>
       <c r="D29" s="6" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="30" spans="2:7" ht="14.25">
@@ -3661,18 +3796,22 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A64C410-895F-4040-A7AB-3F7211AA7FBD}">
-  <dimension ref="B1:N40"/>
+  <dimension ref="B1:N41"/>
   <sheetFormatPr defaultColWidth="11.3984375" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="11.3984375" style="11"/>
-    <col min="2" max="2" width="9.1328125" style="11" customWidth="1"/>
-    <col min="3" max="3" width="8.3984375" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="14.73046875" style="11" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.3984375" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.265625" style="11" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.3984375" style="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.73046875" style="11" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="11.3984375" style="11"/>
+    <col min="2" max="2" width="8.6640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.1328125" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.46484375" style="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.33203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.46484375" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.9296875" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.9296875" style="11" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.1328125" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.265625" style="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.53125" style="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.73046875" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="11.3984375" style="11"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="12.75">
@@ -3703,7 +3842,7 @@
     </row>
     <row r="4" spans="2:12">
       <c r="B4" s="14" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G4" s="14"/>
       <c r="H4" s="14"/>
@@ -3711,42 +3850,42 @@
     </row>
     <row r="5" spans="2:12">
       <c r="B5" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="F5" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="G5" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="H5" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="I5" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="F5" s="15" t="s">
+      <c r="J5" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="G5" s="15" t="s">
+      <c r="K5" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="H5" s="15" t="s">
+      <c r="L5" s="15" t="s">
         <v>59</v>
-      </c>
-      <c r="I5" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="J5" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="K5" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="L5" s="15" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="6" spans="2:12">
       <c r="D6" s="11" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E6" s="11">
         <v>0</v>
@@ -3757,7 +3896,7 @@
     </row>
     <row r="7" spans="2:12">
       <c r="D7" s="11" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E7" s="11">
         <v>0</v>
@@ -3768,7 +3907,7 @@
     </row>
     <row r="8" spans="2:12">
       <c r="D8" s="11" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E8" s="11">
         <v>0</v>
@@ -3779,7 +3918,7 @@
     </row>
     <row r="9" spans="2:12">
       <c r="D9" s="11" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="E9" s="11">
         <v>0</v>
@@ -3788,72 +3927,72 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="2:12">
-      <c r="B12" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="14"/>
+    <row r="10" spans="2:12">
+      <c r="D10" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="E10" s="11">
+        <v>0</v>
+      </c>
+      <c r="F10" s="11">
+        <v>5</v>
+      </c>
     </row>
     <row r="13" spans="2:12">
-      <c r="B13" s="15" t="s">
+      <c r="B13" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="G13" s="14"/>
+      <c r="H13" s="14"/>
+      <c r="I13" s="14"/>
+    </row>
+    <row r="14" spans="2:12">
+      <c r="B14" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="F14" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="C13" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="D13" s="15" t="s">
+      <c r="G14" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="H14" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="E13" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="F13" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="G13" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="H13" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="I13" s="15" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="14" spans="2:12">
-      <c r="D14" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="F14" s="11">
-        <v>2222</v>
-      </c>
-      <c r="G14" s="11" t="s">
-        <v>71</v>
+      <c r="I14" s="15" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="15" spans="2:12">
       <c r="D15" s="11" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F15" s="11">
+        <v>2222</v>
+      </c>
+      <c r="G15" s="11" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12">
+      <c r="D16" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="F16" s="11">
         <v>8888</v>
       </c>
-      <c r="G15" s="11" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="16" spans="2:12" ht="12.75">
-      <c r="B16" s="13"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="13"/>
-      <c r="G16" s="13"/>
-      <c r="H16" s="13"/>
-      <c r="I16" s="13"/>
-      <c r="J16" s="13"/>
+      <c r="G16" s="11" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="17" spans="2:14" ht="12.75">
       <c r="B17" s="13"/>
@@ -3877,20 +4016,16 @@
       <c r="I18" s="13"/>
       <c r="J18" s="13"/>
     </row>
-    <row r="19" spans="2:14" ht="14.25">
-      <c r="B19"/>
-      <c r="C19"/>
-      <c r="D19"/>
-      <c r="E19"/>
-      <c r="F19"/>
-      <c r="G19"/>
-      <c r="H19"/>
-      <c r="I19"/>
-      <c r="J19"/>
-      <c r="K19"/>
-      <c r="L19"/>
-      <c r="M19"/>
-      <c r="N19"/>
+    <row r="19" spans="2:14" ht="12.75">
+      <c r="B19" s="13"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="13"/>
+      <c r="I19" s="13"/>
+      <c r="J19" s="13"/>
     </row>
     <row r="20" spans="2:14" ht="14.25">
       <c r="B20"/>
@@ -4207,6 +4342,21 @@
       <c r="M40"/>
       <c r="N40"/>
     </row>
+    <row r="41" spans="2:14" ht="14.25">
+      <c r="B41"/>
+      <c r="C41"/>
+      <c r="D41"/>
+      <c r="E41"/>
+      <c r="F41"/>
+      <c r="G41"/>
+      <c r="H41"/>
+      <c r="I41"/>
+      <c r="J41"/>
+      <c r="K41"/>
+      <c r="L41"/>
+      <c r="M41"/>
+      <c r="N41"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -4216,1546 +4366,1635 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5EBD23C-EA82-4040-97D7-F532F0547462}">
-  <dimension ref="A2:P93"/>
+  <dimension ref="A2:N102"/>
   <sheetFormatPr defaultColWidth="11.3984375" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="11.3984375" style="11"/>
-    <col min="2" max="2" width="10.59765625" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="11.3984375" style="11"/>
+    <col min="2" max="2" width="12.73046875" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="11.3984375" style="11"/>
+    <col min="5" max="5" width="13.53125" style="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.59765625" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.33203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.3984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.9296875" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.6640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.3984375" style="11"/>
+    <col min="12" max="12" width="17.19921875" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.6640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.73046875" style="11" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="11.3984375" style="11"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:16" ht="17.649999999999999" thickBot="1">
+    <row r="2" spans="1:14" ht="17.649999999999999" thickBot="1">
       <c r="A2" s="13"/>
       <c r="B2" s="20" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="N2" s="20" t="s">
-        <v>82</v>
-      </c>
-      <c r="O2" s="6"/>
-      <c r="P2" s="6"/>
-    </row>
-    <row r="3" spans="1:16" ht="15" thickTop="1" thickBot="1">
+        <v>183</v>
+      </c>
+      <c r="L2" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+    </row>
+    <row r="3" spans="1:14" ht="15" thickTop="1" thickBot="1">
       <c r="A3" s="13"/>
       <c r="B3" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>74</v>
+        <v>184</v>
+      </c>
+      <c r="I3" s="4">
+        <v>2022</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="K3" s="4">
-        <v>2022</v>
+        <v>56</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>60</v>
+        <v>80</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>81</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="O3" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="P3" s="4" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" ht="13.15">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="13.15">
       <c r="A4" s="13"/>
       <c r="B4" s="19" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C4" s="6"/>
-      <c r="G4" s="11" t="s">
-        <v>189</v>
-      </c>
-      <c r="K4" s="11">
+      <c r="F4" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="I4" s="11">
         <v>0.05</v>
       </c>
-      <c r="L4" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="N4" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="O4" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="P4" s="6">
+      <c r="J4" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="M4" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="N4" s="6">
         <v>1055.55</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="13.15">
+    <row r="5" spans="1:14" ht="13.15">
       <c r="A5" s="13"/>
       <c r="B5" s="19" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>190</v>
-      </c>
-      <c r="G5" s="11" t="s">
-        <v>191</v>
-      </c>
-      <c r="K5" s="11">
+        <v>186</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="I5" s="11">
         <v>1</v>
       </c>
-      <c r="L5" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="N5" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="O5" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="P5" s="6">
+      <c r="J5" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="M5" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="N5" s="6">
         <v>3.6</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="13.15">
+    <row r="6" spans="1:14" ht="13.15">
       <c r="A6" s="13"/>
       <c r="B6" s="19" t="s">
-        <v>78</v>
-      </c>
-      <c r="G6" s="11" t="s">
-        <v>192</v>
-      </c>
-      <c r="K6" s="11">
+        <v>74</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="I6" s="11">
         <v>2025</v>
       </c>
-      <c r="N6" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="O6" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="P6" s="6">
+      <c r="L6" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="M6" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="N6" s="6">
         <v>1000</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="13.15">
+    <row r="7" spans="1:14" ht="13.15">
       <c r="A7" s="13"/>
       <c r="B7" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="G7" s="11" t="s">
-        <v>193</v>
-      </c>
-      <c r="K7" s="11">
+        <v>75</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="I7" s="11">
         <v>1</v>
       </c>
-      <c r="N7" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="O7" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="P7" s="6">
+      <c r="L7" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="M7" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="N7" s="6">
         <v>1000</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="13.15">
+    <row r="8" spans="1:14" ht="13.15">
       <c r="A8" s="13"/>
       <c r="B8" s="19" t="s">
-        <v>80</v>
+        <v>76</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>190</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="I8" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="J8" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="K8" s="11">
+        <v>127</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="I8" s="11">
         <v>2.2201</v>
       </c>
-      <c r="N8" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="O8" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="P8" s="6">
+      <c r="L8" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="M8" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="N8" s="6">
         <v>1.05555</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="13.15">
+    <row r="9" spans="1:14" ht="13.15">
       <c r="A9" s="13"/>
       <c r="B9" s="19" t="s">
-        <v>81</v>
+        <v>77</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>190</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="I9" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="J9" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="K9" s="11">
+        <v>127</v>
+      </c>
+      <c r="H9" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="I9" s="11">
         <v>2.1427</v>
       </c>
-      <c r="N9" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="O9" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="P9" s="6">
+      <c r="L9" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="M9" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="N9" s="6">
         <v>4.1868000000000002E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="13.15">
+    <row r="10" spans="1:14" ht="13.15">
       <c r="A10" s="13"/>
       <c r="B10" s="19" t="s">
-        <v>83</v>
+        <v>79</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>190</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="I10" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="J10" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="K10" s="11">
+        <v>127</v>
+      </c>
+      <c r="H10" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="I10" s="11">
         <v>2.077</v>
       </c>
-      <c r="N10" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="O10" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="P10" s="6">
+      <c r="L10" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="M10" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="N10" s="6">
         <v>41.868000000000002</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="13.15">
+    <row r="11" spans="1:14" ht="13.15">
       <c r="A11" s="13"/>
       <c r="B11" s="19" t="s">
-        <v>76</v>
+        <v>72</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>190</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="I11" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="J11" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="K11" s="11">
+        <v>127</v>
+      </c>
+      <c r="H11" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="I11" s="11">
         <v>2.0358000000000001</v>
       </c>
-      <c r="N11" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="O11" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="P11" s="6">
+      <c r="L11" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="M11" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="N11" s="6">
         <v>3.5999999999999999E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="13.15">
+    <row r="12" spans="1:14" ht="13.15">
       <c r="A12" s="13"/>
       <c r="B12" s="19" t="s">
-        <v>87</v>
+        <v>83</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>190</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="I12" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="J12" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="K12" s="11">
+        <v>127</v>
+      </c>
+      <c r="H12" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="I12" s="11">
         <v>1.9870000000000001</v>
       </c>
-      <c r="N12" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="O12" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="P12" s="6">
+      <c r="L12" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="M12" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="N12" s="6">
         <v>1000000</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="13.15">
+    <row r="13" spans="1:14" ht="13.15">
       <c r="A13" s="13"/>
       <c r="B13" s="19" t="s">
-        <v>90</v>
+        <v>86</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>190</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="I13" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="J13" s="11" t="s">
-        <v>145</v>
-      </c>
-      <c r="K13" s="11">
+        <v>127</v>
+      </c>
+      <c r="H13" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="I13" s="11">
         <v>1.9192</v>
       </c>
-      <c r="N13" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="O13" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="P13" s="6">
+      <c r="L13" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="M13" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="N13" s="6">
         <v>1000</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="13.15">
+    <row r="14" spans="1:14" ht="13.15">
       <c r="A14" s="13"/>
       <c r="B14" s="19" t="s">
-        <v>92</v>
+        <v>88</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>190</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="I14" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="J14" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="K14" s="11">
+        <v>127</v>
+      </c>
+      <c r="H14" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="I14" s="11">
         <v>1.8468</v>
       </c>
-      <c r="N14" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="O14" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="P14" s="6">
+      <c r="L14" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="M14" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="N14" s="6">
         <v>5.8615199999999996</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="13.15">
+    <row r="15" spans="1:14" ht="13.15">
       <c r="A15" s="13"/>
       <c r="B15" s="19" t="s">
-        <v>95</v>
+        <v>91</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>190</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="I15" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="J15" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="K15" s="11">
+        <v>127</v>
+      </c>
+      <c r="H15" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="I15" s="11">
         <v>1.7799</v>
       </c>
-      <c r="N15" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="O15" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="P15" s="6">
+      <c r="L15" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="M15" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="N15" s="6">
         <v>1E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="13.15">
+    <row r="16" spans="1:14" ht="13.15">
       <c r="A16" s="13"/>
       <c r="B16" s="19" t="s">
-        <v>98</v>
+        <v>94</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>190</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="I16" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="J16" s="11" t="s">
-        <v>148</v>
-      </c>
-      <c r="K16" s="11">
+        <v>127</v>
+      </c>
+      <c r="H16" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="I16" s="11">
         <v>1.722</v>
       </c>
-      <c r="N16" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="O16" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="P16" s="6">
+      <c r="L16" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="M16" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="N16" s="6">
         <v>1000</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="13.15">
+    <row r="17" spans="1:14" ht="13.15">
       <c r="A17" s="13"/>
       <c r="B17" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="G17" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="H17" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="I17" s="11">
+        <v>1.6836</v>
+      </c>
+      <c r="L17" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="M17" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="N17" s="6">
+        <v>37.68</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="13.15">
+      <c r="B18" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="G18" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="H18" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="I18" s="11">
+        <v>1.6446000000000001</v>
+      </c>
+      <c r="L18" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="M18" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="N18" s="6">
+        <v>2139.4548</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="13.15">
+      <c r="B19" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="G17" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="I17" s="11" t="s">
+      <c r="F19" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="G19" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="H19" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="I19" s="11">
+        <v>1.6102000000000001</v>
+      </c>
+      <c r="L19" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="M19" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="N19" s="6">
+        <v>2.78</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="13.15">
+      <c r="B20" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="G20" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="H20" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="I20" s="11">
+        <v>1.5770999999999999</v>
+      </c>
+      <c r="L20" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="M20" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="N20" s="6">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="13.15">
+      <c r="B21" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="G21" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="H21" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="I21" s="11">
+        <v>1.5488</v>
+      </c>
+      <c r="L21" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="M21" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="N21" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="13.15">
+      <c r="B22" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="G22" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="H22" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="I22" s="11">
+        <v>1.5224</v>
+      </c>
+      <c r="L22" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="M22" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="N22" s="6">
+        <v>31.536000000000001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="13.15">
+      <c r="B23" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="F23" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="G23" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="H23" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="I23" s="11">
+        <v>1.5058</v>
+      </c>
+      <c r="L23" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="M23" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="N23" s="6">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="13.15">
+      <c r="B24" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="G24" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="H24" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="I24" s="11">
+        <v>1.4844999999999999</v>
+      </c>
+      <c r="L24" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="M24" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="N24" s="11">
+        <v>5.8615199999999996</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="13.15">
+      <c r="B25" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="F25" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="G25" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="H25" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="I25" s="11">
+        <v>1.4518</v>
+      </c>
+      <c r="L25" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="M25" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="N25" s="11">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" ht="13.15">
+      <c r="B26" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="F26" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="G26" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="H26" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="I26" s="11">
+        <v>1.4198999999999999</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="13.15">
+      <c r="B27" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="F27" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="G27" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="H27" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="I27" s="11">
+        <v>1.3986000000000001</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" ht="13.15">
+      <c r="B28" s="19" t="s">
+        <v>122</v>
+      </c>
+      <c r="F28" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="G28" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="H28" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="I28" s="11">
+        <v>1.3727</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" ht="13.15">
+      <c r="B29" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="F29" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="G29" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="H29" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="I29" s="11">
+        <v>1.3369</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" ht="13.15">
+      <c r="B30" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="F30" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="G30" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="H30" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="I30" s="11">
+        <v>1.2967</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" ht="13.15">
+      <c r="B31" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="F31" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="G31" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="H31" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="I31" s="11">
+        <v>1.2583</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" ht="13.15">
+      <c r="B32" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="F32" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="G32" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="H32" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="I32" s="11">
+        <v>1.2253000000000001</v>
+      </c>
+    </row>
+    <row r="33" spans="2:9" ht="13.15">
+      <c r="B33" s="19" t="s">
         <v>131</v>
       </c>
-      <c r="J17" s="11" t="s">
+      <c r="F33" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="G33" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="H33" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="I33" s="11">
+        <v>1.2023999999999999</v>
+      </c>
+    </row>
+    <row r="34" spans="2:9" ht="13.15">
+      <c r="B34" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="F34" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="G34" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="H34" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="I34" s="11">
+        <v>1.1931</v>
+      </c>
+    </row>
+    <row r="35" spans="2:9" ht="13.15">
+      <c r="B35" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="F35" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="G35" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="H35" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="I35" s="11">
+        <v>1.1793</v>
+      </c>
+    </row>
+    <row r="36" spans="2:9" ht="13.15">
+      <c r="B36" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="F36" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="G36" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="H36" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="I36" s="11">
+        <v>1.1552</v>
+      </c>
+    </row>
+    <row r="37" spans="2:9" ht="13.15">
+      <c r="B37" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="F37" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="G37" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="H37" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="I37" s="11">
+        <v>1.1334</v>
+      </c>
+    </row>
+    <row r="38" spans="2:9" ht="13.15">
+      <c r="B38" s="19" t="s">
+        <v>137</v>
+      </c>
+      <c r="F38" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="G38" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="H38" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="I38" s="11">
+        <v>1.1136999999999999</v>
+      </c>
+    </row>
+    <row r="39" spans="2:9" ht="13.15">
+      <c r="B39" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="F39" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="G39" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="H39" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="I39" s="11">
+        <v>1.0934999999999999</v>
+      </c>
+    </row>
+    <row r="40" spans="2:9" ht="13.15">
+      <c r="B40" s="19" t="s">
+        <v>139</v>
+      </c>
+      <c r="F40" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="G40" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="H40" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="I40" s="11">
+        <v>1.0831</v>
+      </c>
+    </row>
+    <row r="41" spans="2:9" ht="13.15">
+      <c r="B41" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="F41" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="G41" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="H41" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="I41" s="11">
+        <v>1.0719000000000001</v>
+      </c>
+    </row>
+    <row r="42" spans="2:9" ht="13.15">
+      <c r="B42" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="F42" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="G42" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="H42" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="I42" s="11">
+        <v>1.0519000000000001</v>
+      </c>
+    </row>
+    <row r="43" spans="2:9" ht="13.15">
+      <c r="B43" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="F43" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="G43" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="H43" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="I43" s="11">
+        <v>1.0274000000000001</v>
+      </c>
+    </row>
+    <row r="44" spans="2:9" ht="13.15">
+      <c r="B44" s="19" t="s">
+        <v>143</v>
+      </c>
+      <c r="F44" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="G44" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="H44" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="I44" s="11">
+        <v>1.0091000000000001</v>
+      </c>
+    </row>
+    <row r="45" spans="2:9" ht="13.15">
+      <c r="B45" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="F45" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="G45" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="H45" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="I45" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="2:9" ht="13.15">
+      <c r="B46" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="F46" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="G46" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="H46" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="I46" s="11">
+        <v>0.98960000000000004</v>
+      </c>
+    </row>
+    <row r="47" spans="2:9" ht="13.15">
+      <c r="B47" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="F47" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="G47" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="H47" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="I47" s="11">
+        <v>0.97809999999999997</v>
+      </c>
+    </row>
+    <row r="48" spans="2:9" ht="13.15">
+      <c r="B48" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="F48" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="G48" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="H48" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="I48" s="11">
+        <v>0.96499999999999997</v>
+      </c>
+    </row>
+    <row r="49" spans="2:9" ht="13.15">
+      <c r="B49" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="F49" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="G49" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="H49" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="I49" s="11">
+        <v>0.94910000000000005</v>
+      </c>
+    </row>
+    <row r="50" spans="2:9" ht="13.15">
+      <c r="B50" s="19" t="s">
         <v>149</v>
       </c>
-      <c r="K17" s="11">
-        <v>1.6836</v>
-      </c>
-      <c r="N17" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="O17" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="P17" s="6">
-        <v>37.68</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" ht="13.15">
-      <c r="B18" s="19" t="s">
+      <c r="F50" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="G50" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="H50" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="I50" s="11">
+        <v>0.92969999999999997</v>
+      </c>
+    </row>
+    <row r="51" spans="2:9" ht="13.15">
+      <c r="B51" s="19" t="s">
+        <v>150</v>
+      </c>
+      <c r="F51" s="11" t="str">
+        <f>F46</f>
+        <v>G_CUREX</v>
+      </c>
+      <c r="G51" s="11" t="str">
+        <f t="shared" ref="G51:I51" si="0">G46</f>
+        <v>USD20</v>
+      </c>
+      <c r="H51" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="I51" s="11">
+        <f t="shared" si="0"/>
+        <v>0.98960000000000004</v>
+      </c>
+    </row>
+    <row r="52" spans="2:9" ht="13.15">
+      <c r="B52" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="F52" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="H52" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="I52" s="11">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="53" spans="2:9" ht="13.15">
+      <c r="B53" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="F53" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="H53" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="I53" s="11">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="54" spans="2:9" ht="13.15">
+      <c r="B54" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="F54" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="H54" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="I54" s="11">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="55" spans="2:9">
+      <c r="F55" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="H55" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="I55" s="11">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="56" spans="2:9">
+      <c r="F56" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="H56" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="I56" s="11">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="57" spans="2:9">
+      <c r="F57" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="H57" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="I57" s="11">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="58" spans="2:9">
+      <c r="F58" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="H58" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="I58" s="11">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="59" spans="2:9">
+      <c r="F59" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="H59" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="I59" s="11">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="60" spans="2:9">
+      <c r="F60" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="H60" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="I60" s="11">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="61" spans="2:9">
+      <c r="F61" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="H61" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="I61" s="11">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="62" spans="2:9">
+      <c r="F62" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="H62" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="I62" s="11">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="63" spans="2:9">
+      <c r="F63" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="H63" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="I63" s="11">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="64" spans="2:9">
+      <c r="F64" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="H64" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="I64" s="11">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="65" spans="6:9">
+      <c r="F65" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="H65" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="I65" s="11">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="66" spans="6:9">
+      <c r="F66" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="H66" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="I66" s="11">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="67" spans="6:9">
+      <c r="F67" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="H67" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="I67" s="11">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="68" spans="6:9">
+      <c r="F68" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="H68" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="I68" s="11">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="69" spans="6:9">
+      <c r="F69" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="H69" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="I69" s="11">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="70" spans="6:9">
+      <c r="F70" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="H70" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="I70" s="11">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="71" spans="6:9">
+      <c r="F71" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="H71" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="I71" s="11">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="72" spans="6:9">
+      <c r="F72" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="H72" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="I72" s="11">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="73" spans="6:9">
+      <c r="F73" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="H73" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="I73" s="11">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="74" spans="6:9">
+      <c r="F74" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="H74" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="I74" s="11">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="75" spans="6:9">
+      <c r="F75" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="H75" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="I75" s="11">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="76" spans="6:9">
+      <c r="F76" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="H76" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="I76" s="11">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="77" spans="6:9">
+      <c r="F77" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="H77" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="I77" s="11">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="78" spans="6:9">
+      <c r="F78" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="H78" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="G18" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="I18" s="11" t="s">
+      <c r="I78" s="11">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="79" spans="6:9">
+      <c r="F79" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="H79" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="I79" s="11">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="80" spans="6:9">
+      <c r="F80" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="H80" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="I80" s="11">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="81" spans="6:9">
+      <c r="F81" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="H81" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="I81" s="11">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="82" spans="6:9">
+      <c r="F82" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="H82" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="I82" s="11">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="83" spans="6:9">
+      <c r="F83" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="H83" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="I83" s="11">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="84" spans="6:9">
+      <c r="F84" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="H84" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="I84" s="11">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="85" spans="6:9">
+      <c r="F85" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="H85" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="I85" s="11">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="86" spans="6:9">
+      <c r="F86" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="H86" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="I86" s="11">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="87" spans="6:9">
+      <c r="F87" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="H87" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="I87" s="11">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="88" spans="6:9">
+      <c r="F88" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="H88" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="I88" s="11">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="89" spans="6:9">
+      <c r="F89" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="H89" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="I89" s="11">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="90" spans="6:9">
+      <c r="F90" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="H90" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="I90" s="11">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="91" spans="6:9">
+      <c r="F91" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="H91" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="J18" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="K18" s="11">
-        <v>1.6446000000000001</v>
-      </c>
-      <c r="N18" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="O18" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="P18" s="6">
-        <v>2139.4548</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" ht="13.15">
-      <c r="B19" s="19" t="s">
-        <v>104</v>
-      </c>
-      <c r="G19" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="I19" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="J19" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="K19" s="11">
-        <v>1.6102000000000001</v>
-      </c>
-      <c r="N19" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="O19" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="P19" s="6">
-        <v>2.78</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" ht="13.15">
-      <c r="B20" s="19" t="s">
-        <v>106</v>
-      </c>
-      <c r="G20" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="I20" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="J20" s="11" t="s">
-        <v>152</v>
-      </c>
-      <c r="K20" s="11">
-        <v>1.5770999999999999</v>
-      </c>
-      <c r="N20" s="6" t="s">
+      <c r="I91" s="11">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="92" spans="6:9">
+      <c r="F92" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="H92" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="I92" s="11">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="93" spans="6:9">
+      <c r="F93" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="H93" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="I93" s="11">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="94" spans="6:9">
+      <c r="F94" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="H94" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="I94" s="11">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="95" spans="6:9">
+      <c r="F95" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="H95" s="11" t="str">
+        <f>H51</f>
+        <v>USD21_alt</v>
+      </c>
+      <c r="I95" s="11">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="99" spans="5:10" ht="17.649999999999999" thickBot="1">
+      <c r="E99" s="20" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="100" spans="5:10" ht="15" thickTop="1" thickBot="1">
+      <c r="E100" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="F100" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G100" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="H100" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="I100" s="4">
+        <v>2022</v>
+      </c>
+      <c r="J100" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="101" spans="5:10" ht="14.25">
+      <c r="E101"/>
+      <c r="F101" s="21" t="s">
+        <v>190</v>
+      </c>
+      <c r="G101" s="21" t="s">
         <v>127</v>
       </c>
-      <c r="O20" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="P20" s="6">
-        <v>3.6</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" ht="13.15">
-      <c r="B21" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="G21" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="I21" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="J21" s="11" t="s">
-        <v>153</v>
-      </c>
-      <c r="K21" s="11">
-        <v>1.5488</v>
-      </c>
-      <c r="N21" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="O21" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="P21" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" ht="13.15">
-      <c r="B22" s="19" t="s">
-        <v>111</v>
-      </c>
-      <c r="G22" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="I22" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="J22" s="11" t="s">
-        <v>154</v>
-      </c>
-      <c r="K22" s="11">
-        <v>1.5224</v>
-      </c>
-      <c r="N22" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="O22" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="P22" s="6">
-        <v>31.536000000000001</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" ht="13.15">
-      <c r="B23" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="G23" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="I23" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="J23" s="11" t="s">
-        <v>155</v>
-      </c>
-      <c r="K23" s="11">
-        <v>1.5058</v>
-      </c>
-      <c r="N23" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="O23" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="P23" s="6">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" ht="13.15">
-      <c r="B24" s="19" t="s">
-        <v>117</v>
-      </c>
-      <c r="G24" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="I24" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="J24" s="11" t="s">
-        <v>156</v>
-      </c>
-      <c r="K24" s="11">
-        <v>1.4844999999999999</v>
-      </c>
-      <c r="N24" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="O24" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="P24" s="11">
-        <v>5.8615199999999996</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" ht="13.15">
-      <c r="B25" s="19" t="s">
-        <v>119</v>
-      </c>
-      <c r="G25" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="I25" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="J25" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="K25" s="11">
-        <v>1.4518</v>
-      </c>
-      <c r="N25" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="O25" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="P25" s="11">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" ht="13.15">
-      <c r="B26" s="19" t="s">
-        <v>121</v>
-      </c>
-      <c r="G26" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="I26" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="J26" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="K26" s="11">
-        <v>1.4198999999999999</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" ht="13.15">
-      <c r="B27" s="19" t="s">
-        <v>123</v>
-      </c>
-      <c r="G27" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="I27" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="J27" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="K27" s="11">
-        <v>1.3986000000000001</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" ht="13.15">
-      <c r="B28" s="19" t="s">
-        <v>126</v>
-      </c>
-      <c r="G28" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="I28" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="J28" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="K28" s="11">
-        <v>1.3727</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" ht="13.15">
-      <c r="B29" s="19" t="s">
-        <v>128</v>
-      </c>
-      <c r="G29" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="I29" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="J29" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="K29" s="11">
-        <v>1.3369</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" ht="13.15">
-      <c r="B30" s="19" t="s">
-        <v>129</v>
-      </c>
-      <c r="G30" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="I30" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="J30" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="K30" s="11">
-        <v>1.2967</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" ht="13.15">
-      <c r="B31" s="19" t="s">
-        <v>131</v>
-      </c>
-      <c r="G31" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="I31" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="J31" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="K31" s="11">
-        <v>1.2583</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" ht="13.15">
-      <c r="B32" s="19" t="s">
-        <v>133</v>
-      </c>
-      <c r="G32" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="I32" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="J32" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="K32" s="11">
-        <v>1.2253000000000001</v>
-      </c>
-    </row>
-    <row r="33" spans="2:11" ht="13.15">
-      <c r="B33" s="19" t="s">
-        <v>135</v>
-      </c>
-      <c r="G33" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="I33" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="J33" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="K33" s="11">
-        <v>1.2023999999999999</v>
-      </c>
-    </row>
-    <row r="34" spans="2:11" ht="13.15">
-      <c r="B34" s="19" t="s">
-        <v>137</v>
-      </c>
-      <c r="G34" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="I34" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="J34" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="K34" s="11">
-        <v>1.1931</v>
-      </c>
-    </row>
-    <row r="35" spans="2:11" ht="13.15">
-      <c r="B35" s="19" t="s">
-        <v>138</v>
-      </c>
-      <c r="G35" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="I35" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="J35" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="K35" s="11">
-        <v>1.1793</v>
-      </c>
-    </row>
-    <row r="36" spans="2:11" ht="13.15">
-      <c r="B36" s="19" t="s">
-        <v>139</v>
-      </c>
-      <c r="G36" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="I36" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="J36" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="K36" s="11">
-        <v>1.1552</v>
-      </c>
-    </row>
-    <row r="37" spans="2:11" ht="13.15">
-      <c r="B37" s="19" t="s">
-        <v>140</v>
-      </c>
-      <c r="G37" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="I37" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="J37" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="K37" s="11">
-        <v>1.1334</v>
-      </c>
-    </row>
-    <row r="38" spans="2:11" ht="13.15">
-      <c r="B38" s="19" t="s">
-        <v>141</v>
-      </c>
-      <c r="G38" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="I38" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="J38" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="K38" s="11">
-        <v>1.1136999999999999</v>
-      </c>
-    </row>
-    <row r="39" spans="2:11" ht="13.15">
-      <c r="B39" s="19" t="s">
-        <v>142</v>
-      </c>
-      <c r="G39" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="I39" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="J39" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="K39" s="11">
-        <v>1.0934999999999999</v>
-      </c>
-    </row>
-    <row r="40" spans="2:11" ht="13.15">
-      <c r="B40" s="19" t="s">
-        <v>143</v>
-      </c>
-      <c r="G40" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="I40" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="J40" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="K40" s="11">
-        <v>1.0831</v>
-      </c>
-    </row>
-    <row r="41" spans="2:11" ht="13.15">
-      <c r="B41" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="G41" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="I41" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="J41" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="K41" s="11">
-        <v>1.0719000000000001</v>
-      </c>
-    </row>
-    <row r="42" spans="2:11" ht="13.15">
-      <c r="B42" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="G42" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="I42" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="J42" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="K42" s="11">
-        <v>1.0519000000000001</v>
-      </c>
-    </row>
-    <row r="43" spans="2:11" ht="13.15">
-      <c r="B43" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="G43" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="I43" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="J43" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="K43" s="11">
-        <v>1.0274000000000001</v>
-      </c>
-    </row>
-    <row r="44" spans="2:11" ht="13.15">
-      <c r="B44" s="19" t="s">
-        <v>147</v>
-      </c>
-      <c r="G44" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="I44" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="J44" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="K44" s="11">
-        <v>1.0091000000000001</v>
-      </c>
-    </row>
-    <row r="45" spans="2:11" ht="13.15">
-      <c r="B45" s="19" t="s">
-        <v>148</v>
-      </c>
-      <c r="G45" s="11" t="s">
-        <v>195</v>
-      </c>
-      <c r="I45" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="J45" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="K45" s="11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="2:11" ht="13.15">
-      <c r="B46" s="19" t="s">
-        <v>149</v>
-      </c>
-      <c r="G46" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="I46" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="J46" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="K46" s="11">
-        <v>0.98960000000000004</v>
-      </c>
-    </row>
-    <row r="47" spans="2:11" ht="13.15">
-      <c r="B47" s="19" t="s">
-        <v>150</v>
-      </c>
-      <c r="G47" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="I47" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="J47" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="K47" s="11">
-        <v>0.97809999999999997</v>
-      </c>
-    </row>
-    <row r="48" spans="2:11" ht="13.15">
-      <c r="B48" s="19" t="s">
-        <v>151</v>
-      </c>
-      <c r="G48" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="I48" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="J48" s="11" t="s">
-        <v>137</v>
-      </c>
-      <c r="K48" s="11">
-        <v>0.96499999999999997</v>
-      </c>
-    </row>
-    <row r="49" spans="2:11" ht="13.15">
-      <c r="B49" s="19" t="s">
-        <v>152</v>
-      </c>
-      <c r="G49" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="I49" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="J49" s="11" t="s">
-        <v>138</v>
-      </c>
-      <c r="K49" s="11">
-        <v>0.94910000000000005</v>
-      </c>
-    </row>
-    <row r="50" spans="2:11" ht="13.15">
-      <c r="B50" s="19" t="s">
-        <v>153</v>
-      </c>
-      <c r="G50" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="I50" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="J50" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="K50" s="11">
-        <v>0.92969999999999997</v>
-      </c>
-    </row>
-    <row r="51" spans="2:11" ht="13.15">
-      <c r="B51" s="19" t="s">
-        <v>154</v>
-      </c>
-      <c r="G51" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="J51" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="K51" s="11">
-        <v>7.0000000000000007E-2</v>
-      </c>
-    </row>
-    <row r="52" spans="2:11" ht="13.15">
-      <c r="B52" s="19" t="s">
-        <v>155</v>
-      </c>
-      <c r="G52" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="J52" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="K52" s="11">
-        <v>7.0000000000000007E-2</v>
-      </c>
-    </row>
-    <row r="53" spans="2:11" ht="13.15">
-      <c r="B53" s="19" t="s">
-        <v>156</v>
-      </c>
-      <c r="G53" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="J53" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="K53" s="11">
-        <v>7.0000000000000007E-2</v>
-      </c>
-    </row>
-    <row r="54" spans="2:11" ht="13.15">
-      <c r="B54" s="19" t="s">
-        <v>157</v>
-      </c>
-      <c r="G54" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="J54" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="K54" s="11">
-        <v>7.0000000000000007E-2</v>
-      </c>
-    </row>
-    <row r="55" spans="2:11">
-      <c r="G55" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="J55" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="K55" s="11">
-        <v>7.0000000000000007E-2</v>
-      </c>
-    </row>
-    <row r="56" spans="2:11">
-      <c r="G56" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="J56" s="11" t="s">
-        <v>145</v>
-      </c>
-      <c r="K56" s="11">
-        <v>7.0000000000000007E-2</v>
-      </c>
-    </row>
-    <row r="57" spans="2:11">
-      <c r="G57" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="J57" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="K57" s="11">
-        <v>7.0000000000000007E-2</v>
-      </c>
-    </row>
-    <row r="58" spans="2:11">
-      <c r="G58" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="J58" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="K58" s="11">
-        <v>7.0000000000000007E-2</v>
-      </c>
-    </row>
-    <row r="59" spans="2:11">
-      <c r="G59" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="J59" s="11" t="s">
-        <v>148</v>
-      </c>
-      <c r="K59" s="11">
-        <v>7.0000000000000007E-2</v>
-      </c>
-    </row>
-    <row r="60" spans="2:11">
-      <c r="G60" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="J60" s="11" t="s">
-        <v>149</v>
-      </c>
-      <c r="K60" s="11">
-        <v>7.0000000000000007E-2</v>
-      </c>
-    </row>
-    <row r="61" spans="2:11">
-      <c r="G61" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="J61" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="K61" s="11">
-        <v>7.0000000000000007E-2</v>
-      </c>
-    </row>
-    <row r="62" spans="2:11">
-      <c r="G62" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="J62" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="K62" s="11">
-        <v>7.0000000000000007E-2</v>
-      </c>
-    </row>
-    <row r="63" spans="2:11">
-      <c r="G63" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="J63" s="11" t="s">
-        <v>152</v>
-      </c>
-      <c r="K63" s="11">
-        <v>7.0000000000000007E-2</v>
-      </c>
-    </row>
-    <row r="64" spans="2:11">
-      <c r="G64" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="J64" s="11" t="s">
-        <v>153</v>
-      </c>
-      <c r="K64" s="11">
-        <v>7.0000000000000007E-2</v>
-      </c>
-    </row>
-    <row r="65" spans="7:11">
-      <c r="G65" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="J65" s="11" t="s">
-        <v>154</v>
-      </c>
-      <c r="K65" s="11">
-        <v>7.0000000000000007E-2</v>
-      </c>
-    </row>
-    <row r="66" spans="7:11">
-      <c r="G66" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="J66" s="11" t="s">
-        <v>155</v>
-      </c>
-      <c r="K66" s="11">
-        <v>7.0000000000000007E-2</v>
-      </c>
-    </row>
-    <row r="67" spans="7:11">
-      <c r="G67" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="J67" s="11" t="s">
-        <v>156</v>
-      </c>
-      <c r="K67" s="11">
-        <v>7.0000000000000007E-2</v>
-      </c>
-    </row>
-    <row r="68" spans="7:11">
-      <c r="G68" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="J68" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="K68" s="11">
-        <v>7.0000000000000007E-2</v>
-      </c>
-    </row>
-    <row r="69" spans="7:11">
-      <c r="G69" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="J69" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="K69" s="11">
-        <v>7.0000000000000007E-2</v>
-      </c>
-    </row>
-    <row r="70" spans="7:11">
-      <c r="G70" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="J70" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="K70" s="11">
-        <v>7.0000000000000007E-2</v>
-      </c>
-    </row>
-    <row r="71" spans="7:11">
-      <c r="G71" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="J71" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="K71" s="11">
-        <v>7.0000000000000007E-2</v>
-      </c>
-    </row>
-    <row r="72" spans="7:11">
-      <c r="G72" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="J72" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="K72" s="11">
-        <v>7.0000000000000007E-2</v>
-      </c>
-    </row>
-    <row r="73" spans="7:11">
-      <c r="G73" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="J73" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="K73" s="11">
-        <v>7.0000000000000007E-2</v>
-      </c>
-    </row>
-    <row r="74" spans="7:11">
-      <c r="G74" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="J74" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="K74" s="11">
-        <v>7.0000000000000007E-2</v>
-      </c>
-    </row>
-    <row r="75" spans="7:11">
-      <c r="G75" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="J75" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="K75" s="11">
-        <v>7.0000000000000007E-2</v>
-      </c>
-    </row>
-    <row r="76" spans="7:11">
-      <c r="G76" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="J76" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="K76" s="11">
-        <v>7.0000000000000007E-2</v>
-      </c>
-    </row>
-    <row r="77" spans="7:11">
-      <c r="G77" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="J77" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="K77" s="11">
-        <v>7.0000000000000007E-2</v>
-      </c>
-    </row>
-    <row r="78" spans="7:11">
-      <c r="G78" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="J78" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="K78" s="11">
-        <v>7.0000000000000007E-2</v>
-      </c>
-    </row>
-    <row r="79" spans="7:11">
-      <c r="G79" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="J79" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="K79" s="11">
-        <v>7.0000000000000007E-2</v>
-      </c>
-    </row>
-    <row r="80" spans="7:11">
-      <c r="G80" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="J80" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="K80" s="11">
-        <v>7.0000000000000007E-2</v>
-      </c>
-    </row>
-    <row r="81" spans="7:11">
-      <c r="G81" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="J81" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="K81" s="11">
-        <v>7.0000000000000007E-2</v>
-      </c>
-    </row>
-    <row r="82" spans="7:11">
-      <c r="G82" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="J82" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="K82" s="11">
-        <v>7.0000000000000007E-2</v>
-      </c>
-    </row>
-    <row r="83" spans="7:11">
-      <c r="G83" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="J83" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="K83" s="11">
-        <v>7.0000000000000007E-2</v>
-      </c>
-    </row>
-    <row r="84" spans="7:11">
-      <c r="G84" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="J84" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="K84" s="11">
-        <v>7.0000000000000007E-2</v>
-      </c>
-    </row>
-    <row r="85" spans="7:11">
-      <c r="G85" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="J85" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="K85" s="11">
-        <v>7.0000000000000007E-2</v>
-      </c>
-    </row>
-    <row r="86" spans="7:11">
-      <c r="G86" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="J86" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="K86" s="11">
-        <v>7.0000000000000007E-2</v>
-      </c>
-    </row>
-    <row r="87" spans="7:11">
-      <c r="G87" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="J87" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="K87" s="11">
-        <v>7.0000000000000007E-2</v>
-      </c>
-    </row>
-    <row r="88" spans="7:11">
-      <c r="G88" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="J88" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="K88" s="11">
-        <v>7.0000000000000007E-2</v>
-      </c>
-    </row>
-    <row r="89" spans="7:11">
-      <c r="G89" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="J89" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="K89" s="11">
-        <v>7.0000000000000007E-2</v>
-      </c>
-    </row>
-    <row r="90" spans="7:11">
-      <c r="G90" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="J90" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="K90" s="11">
-        <v>7.0000000000000007E-2</v>
-      </c>
-    </row>
-    <row r="91" spans="7:11">
-      <c r="G91" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="J91" s="11" t="s">
-        <v>137</v>
-      </c>
-      <c r="K91" s="11">
-        <v>7.0000000000000007E-2</v>
-      </c>
-    </row>
-    <row r="92" spans="7:11">
-      <c r="G92" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="J92" s="11" t="s">
-        <v>138</v>
-      </c>
-      <c r="K92" s="11">
-        <v>7.0000000000000007E-2</v>
-      </c>
-    </row>
-    <row r="93" spans="7:11">
-      <c r="G93" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="J93" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="K93" s="11">
+      <c r="H101" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="I101" s="22">
+        <f>1.10926234054354*I40</f>
+        <v>1.201442041042708</v>
+      </c>
+    </row>
+    <row r="102" spans="5:10" ht="14.25">
+      <c r="E102"/>
+      <c r="F102" s="21" t="s">
+        <v>192</v>
+      </c>
+      <c r="G102"/>
+      <c r="H102" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="I102" s="22">
+        <f>I84</f>
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
@@ -5777,26 +6016,26 @@
   <sheetData>
     <row r="3" spans="2:4" ht="17.649999999999999" thickBot="1">
       <c r="B3" s="20" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="2:4" ht="15" thickTop="1" thickBot="1">
       <c r="B4" s="4" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="2:4">
       <c r="B5" s="6" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D5" s="6">
         <v>-1</v>
@@ -5804,10 +6043,10 @@
     </row>
     <row r="6" spans="2:4">
       <c r="B6" s="6" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="D6" s="6">
         <v>1</v>
@@ -5815,10 +6054,10 @@
     </row>
     <row r="7" spans="2:4">
       <c r="B7" s="6" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="D7" s="6">
         <v>1</v>
@@ -5826,10 +6065,10 @@
     </row>
     <row r="8" spans="2:4">
       <c r="B8" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>158</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>162</v>
       </c>
       <c r="D8" s="6">
         <v>1</v>
@@ -5837,10 +6076,10 @@
     </row>
     <row r="9" spans="2:4">
       <c r="B9" s="6" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="D9" s="6">
         <v>1</v>
@@ -5848,10 +6087,10 @@
     </row>
     <row r="10" spans="2:4">
       <c r="B10" s="6" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D10" s="6">
         <v>1</v>
@@ -5859,10 +6098,10 @@
     </row>
     <row r="11" spans="2:4">
       <c r="B11" s="6" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D11" s="6">
         <v>1</v>
@@ -5870,10 +6109,10 @@
     </row>
     <row r="12" spans="2:4">
       <c r="B12" s="6" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="D12" s="6">
         <v>1</v>
@@ -5881,10 +6120,10 @@
     </row>
     <row r="13" spans="2:4">
       <c r="B13" s="6" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D13" s="6">
         <v>1</v>
@@ -5892,10 +6131,10 @@
     </row>
     <row r="14" spans="2:4">
       <c r="B14" s="6" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="D14" s="6">
         <v>2</v>
@@ -5903,10 +6142,10 @@
     </row>
     <row r="15" spans="2:4">
       <c r="B15" s="6" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D15" s="6">
         <v>1</v>
@@ -5914,10 +6153,10 @@
     </row>
     <row r="16" spans="2:4">
       <c r="B16" s="6" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="D16" s="16">
         <v>1.0000000000000001E-5</v>
@@ -5925,10 +6164,10 @@
     </row>
     <row r="17" spans="2:4">
       <c r="B17" s="6" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D17" s="16">
         <v>1.0000000000000001E-5</v>
@@ -5936,10 +6175,10 @@
     </row>
     <row r="18" spans="2:4">
       <c r="B18" s="6" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="D18" s="16">
         <v>1.0000000000000001E-5</v>
@@ -5947,10 +6186,10 @@
     </row>
     <row r="19" spans="2:4">
       <c r="B19" s="6" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="D19" s="16">
         <v>1.0000000000000001E-5</v>
@@ -5958,10 +6197,10 @@
     </row>
     <row r="20" spans="2:4">
       <c r="B20" s="6" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="D20" s="17">
         <v>1</v>
@@ -5969,73 +6208,73 @@
     </row>
     <row r="23" spans="2:4">
       <c r="B23" s="18" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="25" spans="2:4" ht="17.649999999999999" thickBot="1">
       <c r="B25" s="20" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
     </row>
     <row r="26" spans="2:4" ht="15" thickTop="1" thickBot="1">
       <c r="B26" s="4" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
     </row>
     <row r="27" spans="2:4">
       <c r="B27" s="6" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
     </row>
     <row r="28" spans="2:4">
       <c r="B28" s="6" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
     </row>
     <row r="29" spans="2:4">
       <c r="B29" s="6" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
     </row>
     <row r="30" spans="2:4">
       <c r="B30" s="6" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
     </row>
     <row r="31" spans="2:4">
       <c r="B31" s="6" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
     </row>
     <row r="32" spans="2:4">
       <c r="B32" s="6" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="33" spans="2:3">
       <c r="B33" s="6" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_AUS/SysSettings.xlsx
+++ b/VerveStacks_AUS/SysSettings.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_AUS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A59C32A9-14D1-40E0-B69B-2D7CBC55FFDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A16E78AE-CCB1-4893-9C4C-7686A9285C0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2023" uniqueCount="706">
   <si>
     <t>~BookRegions_Map</t>
   </si>
@@ -676,31 +676,1486 @@
     <t>OIL</t>
   </si>
   <si>
+    <t>cap_bnd</t>
+  </si>
+  <si>
     <t>AUS</t>
   </si>
   <si>
     <t>set</t>
   </si>
   <si>
-    <t>elc_spv-AUS</t>
-  </si>
-  <si>
-    <t>solar electricity generation</t>
+    <t>elc_spv_001</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 1</t>
   </si>
   <si>
     <t>TWh</t>
   </si>
   <si>
-    <t>elc_wof-AUS</t>
-  </si>
-  <si>
-    <t>offshore wind electricity generation</t>
-  </si>
-  <si>
-    <t>elc_won-AUS</t>
-  </si>
-  <si>
-    <t>onshore wind electricity generation</t>
+    <t>elc_spv_002</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 2</t>
+  </si>
+  <si>
+    <t>elc_spv_003</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 3</t>
+  </si>
+  <si>
+    <t>elc_spv_004</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 4</t>
+  </si>
+  <si>
+    <t>elc_spv_005</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 5</t>
+  </si>
+  <si>
+    <t>elc_spv_006</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 6</t>
+  </si>
+  <si>
+    <t>elc_spv_007</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 7</t>
+  </si>
+  <si>
+    <t>elc_spv_008</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 8</t>
+  </si>
+  <si>
+    <t>elc_spv_009</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 9</t>
+  </si>
+  <si>
+    <t>elc_spv_010</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 10</t>
+  </si>
+  <si>
+    <t>elc_spv_011</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 11</t>
+  </si>
+  <si>
+    <t>elc_spv_012</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 12</t>
+  </si>
+  <si>
+    <t>elc_spv_013</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 13</t>
+  </si>
+  <si>
+    <t>elc_spv_014</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 14</t>
+  </si>
+  <si>
+    <t>elc_spv_015</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 15</t>
+  </si>
+  <si>
+    <t>elc_spv_016</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 16</t>
+  </si>
+  <si>
+    <t>elc_spv_017</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 17</t>
+  </si>
+  <si>
+    <t>elc_spv_018</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 18</t>
+  </si>
+  <si>
+    <t>elc_spv_019</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 19</t>
+  </si>
+  <si>
+    <t>elc_spv_020</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 20</t>
+  </si>
+  <si>
+    <t>elc_spv_021</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 21</t>
+  </si>
+  <si>
+    <t>elc_spv_022</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 22</t>
+  </si>
+  <si>
+    <t>elc_spv_023</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 23</t>
+  </si>
+  <si>
+    <t>elc_spv_024</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 24</t>
+  </si>
+  <si>
+    <t>elc_spv_025</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 25</t>
+  </si>
+  <si>
+    <t>elc_spv_026</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 26</t>
+  </si>
+  <si>
+    <t>elc_spv_027</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 27</t>
+  </si>
+  <si>
+    <t>elc_spv_028</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 28</t>
+  </si>
+  <si>
+    <t>elc_spv_029</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 29</t>
+  </si>
+  <si>
+    <t>elc_spv_030</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 30</t>
+  </si>
+  <si>
+    <t>elc_spv_031</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 31</t>
+  </si>
+  <si>
+    <t>elc_spv_032</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 32</t>
+  </si>
+  <si>
+    <t>elc_spv_033</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 33</t>
+  </si>
+  <si>
+    <t>elc_spv_034</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 34</t>
+  </si>
+  <si>
+    <t>elc_spv_035</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 35</t>
+  </si>
+  <si>
+    <t>elc_spv_036</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 36</t>
+  </si>
+  <si>
+    <t>elc_spv_037</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 37</t>
+  </si>
+  <si>
+    <t>elc_spv_038</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 38</t>
+  </si>
+  <si>
+    <t>elc_spv_039</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 39</t>
+  </si>
+  <si>
+    <t>elc_spv_040</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 40</t>
+  </si>
+  <si>
+    <t>elc_spv_041</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 41</t>
+  </si>
+  <si>
+    <t>elc_spv_042</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 42</t>
+  </si>
+  <si>
+    <t>elc_spv_043</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 43</t>
+  </si>
+  <si>
+    <t>elc_spv_044</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 44</t>
+  </si>
+  <si>
+    <t>elc_spv_045</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 45</t>
+  </si>
+  <si>
+    <t>elc_spv_046</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 46</t>
+  </si>
+  <si>
+    <t>elc_spv_047</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 47</t>
+  </si>
+  <si>
+    <t>elc_spv_048</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 48</t>
+  </si>
+  <si>
+    <t>elc_spv_049</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 49</t>
+  </si>
+  <si>
+    <t>elc_spv_050</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 50</t>
+  </si>
+  <si>
+    <t>elc_spv_051</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 51</t>
+  </si>
+  <si>
+    <t>elc_spv_052</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 52</t>
+  </si>
+  <si>
+    <t>elc_spv_053</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 53</t>
+  </si>
+  <si>
+    <t>elc_spv_054</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 54</t>
+  </si>
+  <si>
+    <t>elc_spv_055</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 55</t>
+  </si>
+  <si>
+    <t>elc_spv_056</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 56</t>
+  </si>
+  <si>
+    <t>elc_spv_057</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 57</t>
+  </si>
+  <si>
+    <t>elc_spv_058</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 58</t>
+  </si>
+  <si>
+    <t>elc_spv_059</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 59</t>
+  </si>
+  <si>
+    <t>elc_spv_060</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 60</t>
+  </si>
+  <si>
+    <t>elc_spv_061</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 61</t>
+  </si>
+  <si>
+    <t>elc_spv_062</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 62</t>
+  </si>
+  <si>
+    <t>elc_spv_063</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 63</t>
+  </si>
+  <si>
+    <t>elc_spv_064</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 64</t>
+  </si>
+  <si>
+    <t>elc_spv_065</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 65</t>
+  </si>
+  <si>
+    <t>elc_spv_066</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 66</t>
+  </si>
+  <si>
+    <t>elc_spv_067</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 67</t>
+  </si>
+  <si>
+    <t>elc_spv_068</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 68</t>
+  </si>
+  <si>
+    <t>elc_spv_069</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 69</t>
+  </si>
+  <si>
+    <t>elc_spv_070</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 70</t>
+  </si>
+  <si>
+    <t>elc_spv_071</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 71</t>
+  </si>
+  <si>
+    <t>elc_spv_072</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 72</t>
+  </si>
+  <si>
+    <t>elc_spv_073</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 73</t>
+  </si>
+  <si>
+    <t>elc_spv_074</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 74</t>
+  </si>
+  <si>
+    <t>elc_spv_075</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 75</t>
+  </si>
+  <si>
+    <t>elc_spv_076</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 76</t>
+  </si>
+  <si>
+    <t>elc_spv_077</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 77</t>
+  </si>
+  <si>
+    <t>elc_spv_078</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 78</t>
+  </si>
+  <si>
+    <t>elc_spv_079</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 79</t>
+  </si>
+  <si>
+    <t>elc_spv_080</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 80</t>
+  </si>
+  <si>
+    <t>elc_spv_081</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 81</t>
+  </si>
+  <si>
+    <t>elc_spv_082</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 82</t>
+  </si>
+  <si>
+    <t>elc_spv_083</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 83</t>
+  </si>
+  <si>
+    <t>elc_spv_084</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 84</t>
+  </si>
+  <si>
+    <t>elc_spv_085</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 85</t>
+  </si>
+  <si>
+    <t>elc_spv_086</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 86</t>
+  </si>
+  <si>
+    <t>elc_spv_087</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 87</t>
+  </si>
+  <si>
+    <t>elc_spv_088</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 88</t>
+  </si>
+  <si>
+    <t>elc_spv_089</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 89</t>
+  </si>
+  <si>
+    <t>elc_spv_090</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 90</t>
+  </si>
+  <si>
+    <t>elc_spv_091</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 91</t>
+  </si>
+  <si>
+    <t>elc_spv_092</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 92</t>
+  </si>
+  <si>
+    <t>elc_spv_093</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 93</t>
+  </si>
+  <si>
+    <t>elc_spv_094</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 94</t>
+  </si>
+  <si>
+    <t>elc_spv_095</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 95</t>
+  </si>
+  <si>
+    <t>elc_spv_096</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 96</t>
+  </si>
+  <si>
+    <t>elc_spv_097</t>
+  </si>
+  <si>
+    <t>solar electricity generation in cluster -- 97</t>
+  </si>
+  <si>
+    <t>elc_wof_001</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 1</t>
+  </si>
+  <si>
+    <t>elc_wof_002</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 2</t>
+  </si>
+  <si>
+    <t>elc_wof_003</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 3</t>
+  </si>
+  <si>
+    <t>elc_wof_004</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 4</t>
+  </si>
+  <si>
+    <t>elc_wof_005</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 5</t>
+  </si>
+  <si>
+    <t>elc_wof_006</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 6</t>
+  </si>
+  <si>
+    <t>elc_wof_007</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 7</t>
+  </si>
+  <si>
+    <t>elc_wof_008</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 8</t>
+  </si>
+  <si>
+    <t>elc_wof_009</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 9</t>
+  </si>
+  <si>
+    <t>elc_wof_010</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 10</t>
+  </si>
+  <si>
+    <t>elc_wof_011</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 11</t>
+  </si>
+  <si>
+    <t>elc_wof_012</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 12</t>
+  </si>
+  <si>
+    <t>elc_wof_013</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 13</t>
+  </si>
+  <si>
+    <t>elc_wof_014</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 14</t>
+  </si>
+  <si>
+    <t>elc_wof_015</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 15</t>
+  </si>
+  <si>
+    <t>elc_wof_016</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 16</t>
+  </si>
+  <si>
+    <t>elc_wof_017</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 17</t>
+  </si>
+  <si>
+    <t>elc_wof_018</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 18</t>
+  </si>
+  <si>
+    <t>elc_wof_019</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 19</t>
+  </si>
+  <si>
+    <t>elc_wof_020</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 20</t>
+  </si>
+  <si>
+    <t>elc_wof_021</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 21</t>
+  </si>
+  <si>
+    <t>elc_wof_022</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 22</t>
+  </si>
+  <si>
+    <t>elc_wof_023</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 23</t>
+  </si>
+  <si>
+    <t>elc_wof_024</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 24</t>
+  </si>
+  <si>
+    <t>elc_wof_025</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 25</t>
+  </si>
+  <si>
+    <t>elc_wof_026</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 26</t>
+  </si>
+  <si>
+    <t>elc_wof_027</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 27</t>
+  </si>
+  <si>
+    <t>elc_wof_028</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 28</t>
+  </si>
+  <si>
+    <t>elc_wof_029</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 29</t>
+  </si>
+  <si>
+    <t>elc_wof_030</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 30</t>
+  </si>
+  <si>
+    <t>elc_wof_031</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 31</t>
+  </si>
+  <si>
+    <t>elc_wof_032</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 32</t>
+  </si>
+  <si>
+    <t>elc_wof_033</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 33</t>
+  </si>
+  <si>
+    <t>elc_wof_034</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 34</t>
+  </si>
+  <si>
+    <t>elc_wof_035</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 35</t>
+  </si>
+  <si>
+    <t>elc_wof_036</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 36</t>
+  </si>
+  <si>
+    <t>elc_wof_037</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 37</t>
+  </si>
+  <si>
+    <t>elc_wof_038</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 38</t>
+  </si>
+  <si>
+    <t>elc_wof_039</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 39</t>
+  </si>
+  <si>
+    <t>elc_wof_040</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 40</t>
+  </si>
+  <si>
+    <t>elc_wof_041</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 41</t>
+  </si>
+  <si>
+    <t>elc_wof_042</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 42</t>
+  </si>
+  <si>
+    <t>elc_wof_043</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 43</t>
+  </si>
+  <si>
+    <t>elc_wof_044</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 44</t>
+  </si>
+  <si>
+    <t>elc_wof_045</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 45</t>
+  </si>
+  <si>
+    <t>elc_wof_046</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 46</t>
+  </si>
+  <si>
+    <t>elc_wof_047</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 47</t>
+  </si>
+  <si>
+    <t>elc_wof_048</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 48</t>
+  </si>
+  <si>
+    <t>elc_wof_049</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 49</t>
+  </si>
+  <si>
+    <t>elc_wof_050</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 50</t>
+  </si>
+  <si>
+    <t>elc_wof_051</t>
+  </si>
+  <si>
+    <t>wind offshore electricity generation in cluster -- 51</t>
+  </si>
+  <si>
+    <t>elc_won_001</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 1</t>
+  </si>
+  <si>
+    <t>elc_won_002</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 2</t>
+  </si>
+  <si>
+    <t>elc_won_003</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 3</t>
+  </si>
+  <si>
+    <t>elc_won_004</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 4</t>
+  </si>
+  <si>
+    <t>elc_won_005</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 5</t>
+  </si>
+  <si>
+    <t>elc_won_006</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 6</t>
+  </si>
+  <si>
+    <t>elc_won_007</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 7</t>
+  </si>
+  <si>
+    <t>elc_won_008</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 8</t>
+  </si>
+  <si>
+    <t>elc_won_009</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 9</t>
+  </si>
+  <si>
+    <t>elc_won_010</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 10</t>
+  </si>
+  <si>
+    <t>elc_won_011</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 11</t>
+  </si>
+  <si>
+    <t>elc_won_012</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 12</t>
+  </si>
+  <si>
+    <t>elc_won_013</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 13</t>
+  </si>
+  <si>
+    <t>elc_won_014</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 14</t>
+  </si>
+  <si>
+    <t>elc_won_015</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 15</t>
+  </si>
+  <si>
+    <t>elc_won_016</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 16</t>
+  </si>
+  <si>
+    <t>elc_won_017</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 17</t>
+  </si>
+  <si>
+    <t>elc_won_018</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 18</t>
+  </si>
+  <si>
+    <t>elc_won_019</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 19</t>
+  </si>
+  <si>
+    <t>elc_won_020</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 20</t>
+  </si>
+  <si>
+    <t>elc_won_021</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 21</t>
+  </si>
+  <si>
+    <t>elc_won_022</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 22</t>
+  </si>
+  <si>
+    <t>elc_won_023</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 23</t>
+  </si>
+  <si>
+    <t>elc_won_024</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 24</t>
+  </si>
+  <si>
+    <t>elc_won_025</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 25</t>
+  </si>
+  <si>
+    <t>elc_won_026</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 26</t>
+  </si>
+  <si>
+    <t>elc_won_027</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 27</t>
+  </si>
+  <si>
+    <t>elc_won_028</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 28</t>
+  </si>
+  <si>
+    <t>elc_won_029</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 29</t>
+  </si>
+  <si>
+    <t>elc_won_030</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 30</t>
+  </si>
+  <si>
+    <t>elc_won_031</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 31</t>
+  </si>
+  <si>
+    <t>elc_won_032</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 32</t>
+  </si>
+  <si>
+    <t>elc_won_033</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 33</t>
+  </si>
+  <si>
+    <t>elc_won_034</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 34</t>
+  </si>
+  <si>
+    <t>elc_won_035</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 35</t>
+  </si>
+  <si>
+    <t>elc_won_036</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 36</t>
+  </si>
+  <si>
+    <t>elc_won_037</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 37</t>
+  </si>
+  <si>
+    <t>elc_won_038</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 38</t>
+  </si>
+  <si>
+    <t>elc_won_039</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 39</t>
+  </si>
+  <si>
+    <t>elc_won_040</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 40</t>
+  </si>
+  <si>
+    <t>elc_won_041</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 41</t>
+  </si>
+  <si>
+    <t>elc_won_042</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 42</t>
+  </si>
+  <si>
+    <t>elc_won_043</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 43</t>
+  </si>
+  <si>
+    <t>elc_won_044</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 44</t>
+  </si>
+  <si>
+    <t>elc_won_045</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 45</t>
+  </si>
+  <si>
+    <t>elc_won_046</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 46</t>
+  </si>
+  <si>
+    <t>elc_won_047</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 47</t>
+  </si>
+  <si>
+    <t>elc_won_048</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 48</t>
+  </si>
+  <si>
+    <t>elc_won_049</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 49</t>
+  </si>
+  <si>
+    <t>elc_won_050</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 50</t>
+  </si>
+  <si>
+    <t>elc_won_051</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 51</t>
+  </si>
+  <si>
+    <t>elc_won_052</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 52</t>
+  </si>
+  <si>
+    <t>elc_won_053</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 53</t>
+  </si>
+  <si>
+    <t>elc_won_054</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 54</t>
+  </si>
+  <si>
+    <t>elc_won_055</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 55</t>
+  </si>
+  <si>
+    <t>elc_won_056</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 56</t>
+  </si>
+  <si>
+    <t>elc_won_057</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 57</t>
+  </si>
+  <si>
+    <t>elc_won_058</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 58</t>
+  </si>
+  <si>
+    <t>elc_won_059</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 59</t>
+  </si>
+  <si>
+    <t>elc_won_060</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 60</t>
+  </si>
+  <si>
+    <t>elc_won_061</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 61</t>
+  </si>
+  <si>
+    <t>elc_won_062</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 62</t>
+  </si>
+  <si>
+    <t>elc_won_063</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 63</t>
+  </si>
+  <si>
+    <t>elc_won_064</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 64</t>
+  </si>
+  <si>
+    <t>elc_won_065</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 65</t>
+  </si>
+  <si>
+    <t>elc_won_066</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 66</t>
+  </si>
+  <si>
+    <t>elc_won_067</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 67</t>
+  </si>
+  <si>
+    <t>elc_won_068</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 68</t>
+  </si>
+  <si>
+    <t>elc_won_069</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 69</t>
+  </si>
+  <si>
+    <t>elc_won_070</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 70</t>
+  </si>
+  <si>
+    <t>elc_won_071</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 71</t>
+  </si>
+  <si>
+    <t>elc_won_072</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 72</t>
+  </si>
+  <si>
+    <t>elc_won_073</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 73</t>
+  </si>
+  <si>
+    <t>elc_won_074</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 74</t>
+  </si>
+  <si>
+    <t>elc_won_075</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 75</t>
+  </si>
+  <si>
+    <t>elc_won_076</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 76</t>
+  </si>
+  <si>
+    <t>elc_won_077</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 77</t>
+  </si>
+  <si>
+    <t>elc_won_078</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 78</t>
+  </si>
+  <si>
+    <t>elc_won_079</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 79</t>
+  </si>
+  <si>
+    <t>elc_won_080</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 80</t>
+  </si>
+  <si>
+    <t>elc_won_081</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 81</t>
+  </si>
+  <si>
+    <t>elc_won_082</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 82</t>
+  </si>
+  <si>
+    <t>elc_won_083</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 83</t>
+  </si>
+  <si>
+    <t>elc_won_084</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 84</t>
+  </si>
+  <si>
+    <t>elc_won_085</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 85</t>
+  </si>
+  <si>
+    <t>elc_won_086</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 86</t>
+  </si>
+  <si>
+    <t>elc_won_087</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 87</t>
+  </si>
+  <si>
+    <t>elc_won_088</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 88</t>
+  </si>
+  <si>
+    <t>elc_won_089</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 89</t>
+  </si>
+  <si>
+    <t>elc_won_090</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 90</t>
+  </si>
+  <si>
+    <t>elc_won_091</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 91</t>
+  </si>
+  <si>
+    <t>elc_won_092</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 92</t>
+  </si>
+  <si>
+    <t>elc_won_093</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 93</t>
+  </si>
+  <si>
+    <t>elc_won_094</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 94</t>
+  </si>
+  <si>
+    <t>elc_won_095</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 95</t>
+  </si>
+  <si>
+    <t>elc_won_096</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 96</t>
+  </si>
+  <si>
+    <t>elc_won_097</t>
+  </si>
+  <si>
+    <t>onshore wind electricity generation in cluster -- 97</t>
   </si>
 </sst>
 </file>
@@ -3091,7 +4546,7 @@
         <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F4" t="s">
         <v>36</v>
@@ -3116,7 +4571,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2F298A9-BCD9-4ABF-BE3B-9D1BDD3E7001}">
-  <dimension ref="B3:R24"/>
+  <dimension ref="B3:R249"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="11.19921875" bestFit="1" customWidth="1"/>
@@ -3174,7 +4629,7 @@
         <v>16</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N4" s="5" t="s">
         <v>10</v>
@@ -3206,10 +4661,10 @@
         <v>17</v>
       </c>
       <c r="N5" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O5" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P5" t="s">
         <v>25</v>
@@ -3218,7 +4673,7 @@
         <v>35</v>
       </c>
       <c r="R5" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="6" spans="2:18">
@@ -3235,10 +4690,10 @@
         <v>17</v>
       </c>
       <c r="N6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P6" t="s">
         <v>25</v>
@@ -3247,7 +4702,7 @@
         <v>35</v>
       </c>
       <c r="R6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="7" spans="2:18">
@@ -3264,10 +4719,10 @@
         <v>17</v>
       </c>
       <c r="N7" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="O7" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P7" t="s">
         <v>25</v>
@@ -3276,7 +4731,7 @@
         <v>35</v>
       </c>
       <c r="R7" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="8" spans="2:18">
@@ -3289,6 +4744,24 @@
       <c r="E8" t="s">
         <v>18</v>
       </c>
+      <c r="M8" t="s">
+        <v>17</v>
+      </c>
+      <c r="N8" t="s">
+        <v>222</v>
+      </c>
+      <c r="O8" t="s">
+        <v>223</v>
+      </c>
+      <c r="P8" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>35</v>
+      </c>
+      <c r="R8" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="9" spans="2:18">
       <c r="B9" t="s">
@@ -3300,6 +4773,24 @@
       <c r="E9" t="s">
         <v>18</v>
       </c>
+      <c r="M9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N9" t="s">
+        <v>224</v>
+      </c>
+      <c r="O9" t="s">
+        <v>225</v>
+      </c>
+      <c r="P9" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>35</v>
+      </c>
+      <c r="R9" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="10" spans="2:18">
       <c r="B10" t="s">
@@ -3311,6 +4802,24 @@
       <c r="E10" t="s">
         <v>18</v>
       </c>
+      <c r="M10" t="s">
+        <v>17</v>
+      </c>
+      <c r="N10" t="s">
+        <v>226</v>
+      </c>
+      <c r="O10" t="s">
+        <v>227</v>
+      </c>
+      <c r="P10" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>35</v>
+      </c>
+      <c r="R10" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="11" spans="2:18">
       <c r="B11" t="s">
@@ -3322,6 +4831,24 @@
       <c r="E11" t="s">
         <v>18</v>
       </c>
+      <c r="M11" t="s">
+        <v>17</v>
+      </c>
+      <c r="N11" t="s">
+        <v>228</v>
+      </c>
+      <c r="O11" t="s">
+        <v>229</v>
+      </c>
+      <c r="P11" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>35</v>
+      </c>
+      <c r="R11" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="12" spans="2:18">
       <c r="B12" t="s">
@@ -3333,6 +4860,24 @@
       <c r="E12" t="s">
         <v>18</v>
       </c>
+      <c r="M12" t="s">
+        <v>17</v>
+      </c>
+      <c r="N12" t="s">
+        <v>230</v>
+      </c>
+      <c r="O12" t="s">
+        <v>231</v>
+      </c>
+      <c r="P12" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>35</v>
+      </c>
+      <c r="R12" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="13" spans="2:18">
       <c r="B13" t="s">
@@ -3344,6 +4889,24 @@
       <c r="E13" t="s">
         <v>18</v>
       </c>
+      <c r="M13" t="s">
+        <v>17</v>
+      </c>
+      <c r="N13" t="s">
+        <v>232</v>
+      </c>
+      <c r="O13" t="s">
+        <v>233</v>
+      </c>
+      <c r="P13" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>35</v>
+      </c>
+      <c r="R13" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="14" spans="2:18">
       <c r="B14" t="s">
@@ -3358,6 +4921,24 @@
       <c r="E14" t="s">
         <v>18</v>
       </c>
+      <c r="M14" t="s">
+        <v>17</v>
+      </c>
+      <c r="N14" t="s">
+        <v>234</v>
+      </c>
+      <c r="O14" t="s">
+        <v>235</v>
+      </c>
+      <c r="P14" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>35</v>
+      </c>
+      <c r="R14" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="15" spans="2:18">
       <c r="B15" t="s">
@@ -3372,6 +4953,24 @@
       <c r="E15" t="s">
         <v>18</v>
       </c>
+      <c r="M15" t="s">
+        <v>17</v>
+      </c>
+      <c r="N15" t="s">
+        <v>236</v>
+      </c>
+      <c r="O15" t="s">
+        <v>237</v>
+      </c>
+      <c r="P15" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>35</v>
+      </c>
+      <c r="R15" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="16" spans="2:18">
       <c r="B16" t="s">
@@ -3395,8 +4994,26 @@
       <c r="I16" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="17" spans="2:7">
+      <c r="M16" t="s">
+        <v>17</v>
+      </c>
+      <c r="N16" t="s">
+        <v>238</v>
+      </c>
+      <c r="O16" t="s">
+        <v>239</v>
+      </c>
+      <c r="P16" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>35</v>
+      </c>
+      <c r="R16" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="17" spans="2:18">
       <c r="B17" t="s">
         <v>34</v>
       </c>
@@ -3409,8 +5026,26 @@
       <c r="E17" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="18" spans="2:7">
+      <c r="M17" t="s">
+        <v>17</v>
+      </c>
+      <c r="N17" t="s">
+        <v>240</v>
+      </c>
+      <c r="O17" t="s">
+        <v>241</v>
+      </c>
+      <c r="P17" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>35</v>
+      </c>
+      <c r="R17" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="18" spans="2:18">
       <c r="B18" t="s">
         <v>34</v>
       </c>
@@ -3423,8 +5058,26 @@
       <c r="E18" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="19" spans="2:7">
+      <c r="M18" t="s">
+        <v>17</v>
+      </c>
+      <c r="N18" t="s">
+        <v>242</v>
+      </c>
+      <c r="O18" t="s">
+        <v>243</v>
+      </c>
+      <c r="P18" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>35</v>
+      </c>
+      <c r="R18" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="19" spans="2:18">
       <c r="B19" t="s">
         <v>34</v>
       </c>
@@ -3437,8 +5090,26 @@
       <c r="E19" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="20" spans="2:7">
+      <c r="M19" t="s">
+        <v>17</v>
+      </c>
+      <c r="N19" t="s">
+        <v>244</v>
+      </c>
+      <c r="O19" t="s">
+        <v>245</v>
+      </c>
+      <c r="P19" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>35</v>
+      </c>
+      <c r="R19" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="20" spans="2:18">
       <c r="B20" t="s">
         <v>34</v>
       </c>
@@ -3451,8 +5122,26 @@
       <c r="E20" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="21" spans="2:7">
+      <c r="M20" t="s">
+        <v>17</v>
+      </c>
+      <c r="N20" t="s">
+        <v>246</v>
+      </c>
+      <c r="O20" t="s">
+        <v>247</v>
+      </c>
+      <c r="P20" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>35</v>
+      </c>
+      <c r="R20" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="21" spans="2:18">
       <c r="B21" t="s">
         <v>17</v>
       </c>
@@ -3471,8 +5160,26 @@
       <c r="G21" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="22" spans="2:7">
+      <c r="M21" t="s">
+        <v>17</v>
+      </c>
+      <c r="N21" t="s">
+        <v>248</v>
+      </c>
+      <c r="O21" t="s">
+        <v>249</v>
+      </c>
+      <c r="P21" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>35</v>
+      </c>
+      <c r="R21" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="22" spans="2:18">
       <c r="B22" t="s">
         <v>193</v>
       </c>
@@ -3485,8 +5192,26 @@
       <c r="E22" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="23" spans="2:7">
+      <c r="M22" t="s">
+        <v>17</v>
+      </c>
+      <c r="N22" t="s">
+        <v>250</v>
+      </c>
+      <c r="O22" t="s">
+        <v>251</v>
+      </c>
+      <c r="P22" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>35</v>
+      </c>
+      <c r="R22" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="23" spans="2:18">
       <c r="B23" t="s">
         <v>193</v>
       </c>
@@ -3496,8 +5221,26 @@
       <c r="E23" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="24" spans="2:7">
+      <c r="M23" t="s">
+        <v>17</v>
+      </c>
+      <c r="N23" t="s">
+        <v>252</v>
+      </c>
+      <c r="O23" t="s">
+        <v>253</v>
+      </c>
+      <c r="P23" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>35</v>
+      </c>
+      <c r="R23" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="24" spans="2:18">
       <c r="B24" t="s">
         <v>193</v>
       </c>
@@ -3506,6 +5249,4524 @@
       </c>
       <c r="E24" t="s">
         <v>196</v>
+      </c>
+      <c r="M24" t="s">
+        <v>17</v>
+      </c>
+      <c r="N24" t="s">
+        <v>254</v>
+      </c>
+      <c r="O24" t="s">
+        <v>255</v>
+      </c>
+      <c r="P24" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>35</v>
+      </c>
+      <c r="R24" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="25" spans="2:18">
+      <c r="M25" t="s">
+        <v>17</v>
+      </c>
+      <c r="N25" t="s">
+        <v>256</v>
+      </c>
+      <c r="O25" t="s">
+        <v>257</v>
+      </c>
+      <c r="P25" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>35</v>
+      </c>
+      <c r="R25" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="26" spans="2:18">
+      <c r="M26" t="s">
+        <v>17</v>
+      </c>
+      <c r="N26" t="s">
+        <v>258</v>
+      </c>
+      <c r="O26" t="s">
+        <v>259</v>
+      </c>
+      <c r="P26" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>35</v>
+      </c>
+      <c r="R26" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="27" spans="2:18">
+      <c r="M27" t="s">
+        <v>17</v>
+      </c>
+      <c r="N27" t="s">
+        <v>260</v>
+      </c>
+      <c r="O27" t="s">
+        <v>261</v>
+      </c>
+      <c r="P27" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>35</v>
+      </c>
+      <c r="R27" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="28" spans="2:18">
+      <c r="M28" t="s">
+        <v>17</v>
+      </c>
+      <c r="N28" t="s">
+        <v>262</v>
+      </c>
+      <c r="O28" t="s">
+        <v>263</v>
+      </c>
+      <c r="P28" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>35</v>
+      </c>
+      <c r="R28" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="29" spans="2:18">
+      <c r="M29" t="s">
+        <v>17</v>
+      </c>
+      <c r="N29" t="s">
+        <v>264</v>
+      </c>
+      <c r="O29" t="s">
+        <v>265</v>
+      </c>
+      <c r="P29" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>35</v>
+      </c>
+      <c r="R29" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="30" spans="2:18">
+      <c r="M30" t="s">
+        <v>17</v>
+      </c>
+      <c r="N30" t="s">
+        <v>266</v>
+      </c>
+      <c r="O30" t="s">
+        <v>267</v>
+      </c>
+      <c r="P30" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>35</v>
+      </c>
+      <c r="R30" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="31" spans="2:18">
+      <c r="M31" t="s">
+        <v>17</v>
+      </c>
+      <c r="N31" t="s">
+        <v>268</v>
+      </c>
+      <c r="O31" t="s">
+        <v>269</v>
+      </c>
+      <c r="P31" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>35</v>
+      </c>
+      <c r="R31" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="32" spans="2:18">
+      <c r="M32" t="s">
+        <v>17</v>
+      </c>
+      <c r="N32" t="s">
+        <v>270</v>
+      </c>
+      <c r="O32" t="s">
+        <v>271</v>
+      </c>
+      <c r="P32" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>35</v>
+      </c>
+      <c r="R32" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="33" spans="13:18">
+      <c r="M33" t="s">
+        <v>17</v>
+      </c>
+      <c r="N33" t="s">
+        <v>272</v>
+      </c>
+      <c r="O33" t="s">
+        <v>273</v>
+      </c>
+      <c r="P33" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>35</v>
+      </c>
+      <c r="R33" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="34" spans="13:18">
+      <c r="M34" t="s">
+        <v>17</v>
+      </c>
+      <c r="N34" t="s">
+        <v>274</v>
+      </c>
+      <c r="O34" t="s">
+        <v>275</v>
+      </c>
+      <c r="P34" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>35</v>
+      </c>
+      <c r="R34" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="35" spans="13:18">
+      <c r="M35" t="s">
+        <v>17</v>
+      </c>
+      <c r="N35" t="s">
+        <v>276</v>
+      </c>
+      <c r="O35" t="s">
+        <v>277</v>
+      </c>
+      <c r="P35" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>35</v>
+      </c>
+      <c r="R35" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="36" spans="13:18">
+      <c r="M36" t="s">
+        <v>17</v>
+      </c>
+      <c r="N36" t="s">
+        <v>278</v>
+      </c>
+      <c r="O36" t="s">
+        <v>279</v>
+      </c>
+      <c r="P36" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>35</v>
+      </c>
+      <c r="R36" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="37" spans="13:18">
+      <c r="M37" t="s">
+        <v>17</v>
+      </c>
+      <c r="N37" t="s">
+        <v>280</v>
+      </c>
+      <c r="O37" t="s">
+        <v>281</v>
+      </c>
+      <c r="P37" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>35</v>
+      </c>
+      <c r="R37" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="38" spans="13:18">
+      <c r="M38" t="s">
+        <v>17</v>
+      </c>
+      <c r="N38" t="s">
+        <v>282</v>
+      </c>
+      <c r="O38" t="s">
+        <v>283</v>
+      </c>
+      <c r="P38" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>35</v>
+      </c>
+      <c r="R38" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="39" spans="13:18">
+      <c r="M39" t="s">
+        <v>17</v>
+      </c>
+      <c r="N39" t="s">
+        <v>284</v>
+      </c>
+      <c r="O39" t="s">
+        <v>285</v>
+      </c>
+      <c r="P39" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>35</v>
+      </c>
+      <c r="R39" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="40" spans="13:18">
+      <c r="M40" t="s">
+        <v>17</v>
+      </c>
+      <c r="N40" t="s">
+        <v>286</v>
+      </c>
+      <c r="O40" t="s">
+        <v>287</v>
+      </c>
+      <c r="P40" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>35</v>
+      </c>
+      <c r="R40" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="41" spans="13:18">
+      <c r="M41" t="s">
+        <v>17</v>
+      </c>
+      <c r="N41" t="s">
+        <v>288</v>
+      </c>
+      <c r="O41" t="s">
+        <v>289</v>
+      </c>
+      <c r="P41" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>35</v>
+      </c>
+      <c r="R41" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="42" spans="13:18">
+      <c r="M42" t="s">
+        <v>17</v>
+      </c>
+      <c r="N42" t="s">
+        <v>290</v>
+      </c>
+      <c r="O42" t="s">
+        <v>291</v>
+      </c>
+      <c r="P42" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>35</v>
+      </c>
+      <c r="R42" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="43" spans="13:18">
+      <c r="M43" t="s">
+        <v>17</v>
+      </c>
+      <c r="N43" t="s">
+        <v>292</v>
+      </c>
+      <c r="O43" t="s">
+        <v>293</v>
+      </c>
+      <c r="P43" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>35</v>
+      </c>
+      <c r="R43" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="44" spans="13:18">
+      <c r="M44" t="s">
+        <v>17</v>
+      </c>
+      <c r="N44" t="s">
+        <v>294</v>
+      </c>
+      <c r="O44" t="s">
+        <v>295</v>
+      </c>
+      <c r="P44" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>35</v>
+      </c>
+      <c r="R44" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="45" spans="13:18">
+      <c r="M45" t="s">
+        <v>17</v>
+      </c>
+      <c r="N45" t="s">
+        <v>296</v>
+      </c>
+      <c r="O45" t="s">
+        <v>297</v>
+      </c>
+      <c r="P45" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>35</v>
+      </c>
+      <c r="R45" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="46" spans="13:18">
+      <c r="M46" t="s">
+        <v>17</v>
+      </c>
+      <c r="N46" t="s">
+        <v>298</v>
+      </c>
+      <c r="O46" t="s">
+        <v>299</v>
+      </c>
+      <c r="P46" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>35</v>
+      </c>
+      <c r="R46" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="47" spans="13:18">
+      <c r="M47" t="s">
+        <v>17</v>
+      </c>
+      <c r="N47" t="s">
+        <v>300</v>
+      </c>
+      <c r="O47" t="s">
+        <v>301</v>
+      </c>
+      <c r="P47" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>35</v>
+      </c>
+      <c r="R47" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="48" spans="13:18">
+      <c r="M48" t="s">
+        <v>17</v>
+      </c>
+      <c r="N48" t="s">
+        <v>302</v>
+      </c>
+      <c r="O48" t="s">
+        <v>303</v>
+      </c>
+      <c r="P48" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>35</v>
+      </c>
+      <c r="R48" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="49" spans="13:18">
+      <c r="M49" t="s">
+        <v>17</v>
+      </c>
+      <c r="N49" t="s">
+        <v>304</v>
+      </c>
+      <c r="O49" t="s">
+        <v>305</v>
+      </c>
+      <c r="P49" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>35</v>
+      </c>
+      <c r="R49" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="50" spans="13:18">
+      <c r="M50" t="s">
+        <v>17</v>
+      </c>
+      <c r="N50" t="s">
+        <v>306</v>
+      </c>
+      <c r="O50" t="s">
+        <v>307</v>
+      </c>
+      <c r="P50" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>35</v>
+      </c>
+      <c r="R50" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="51" spans="13:18">
+      <c r="M51" t="s">
+        <v>17</v>
+      </c>
+      <c r="N51" t="s">
+        <v>308</v>
+      </c>
+      <c r="O51" t="s">
+        <v>309</v>
+      </c>
+      <c r="P51" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>35</v>
+      </c>
+      <c r="R51" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="52" spans="13:18">
+      <c r="M52" t="s">
+        <v>17</v>
+      </c>
+      <c r="N52" t="s">
+        <v>310</v>
+      </c>
+      <c r="O52" t="s">
+        <v>311</v>
+      </c>
+      <c r="P52" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>35</v>
+      </c>
+      <c r="R52" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="53" spans="13:18">
+      <c r="M53" t="s">
+        <v>17</v>
+      </c>
+      <c r="N53" t="s">
+        <v>312</v>
+      </c>
+      <c r="O53" t="s">
+        <v>313</v>
+      </c>
+      <c r="P53" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>35</v>
+      </c>
+      <c r="R53" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="54" spans="13:18">
+      <c r="M54" t="s">
+        <v>17</v>
+      </c>
+      <c r="N54" t="s">
+        <v>314</v>
+      </c>
+      <c r="O54" t="s">
+        <v>315</v>
+      </c>
+      <c r="P54" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>35</v>
+      </c>
+      <c r="R54" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="55" spans="13:18">
+      <c r="M55" t="s">
+        <v>17</v>
+      </c>
+      <c r="N55" t="s">
+        <v>316</v>
+      </c>
+      <c r="O55" t="s">
+        <v>317</v>
+      </c>
+      <c r="P55" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>35</v>
+      </c>
+      <c r="R55" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="56" spans="13:18">
+      <c r="M56" t="s">
+        <v>17</v>
+      </c>
+      <c r="N56" t="s">
+        <v>318</v>
+      </c>
+      <c r="O56" t="s">
+        <v>319</v>
+      </c>
+      <c r="P56" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>35</v>
+      </c>
+      <c r="R56" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="57" spans="13:18">
+      <c r="M57" t="s">
+        <v>17</v>
+      </c>
+      <c r="N57" t="s">
+        <v>320</v>
+      </c>
+      <c r="O57" t="s">
+        <v>321</v>
+      </c>
+      <c r="P57" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>35</v>
+      </c>
+      <c r="R57" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="58" spans="13:18">
+      <c r="M58" t="s">
+        <v>17</v>
+      </c>
+      <c r="N58" t="s">
+        <v>322</v>
+      </c>
+      <c r="O58" t="s">
+        <v>323</v>
+      </c>
+      <c r="P58" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>35</v>
+      </c>
+      <c r="R58" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="59" spans="13:18">
+      <c r="M59" t="s">
+        <v>17</v>
+      </c>
+      <c r="N59" t="s">
+        <v>324</v>
+      </c>
+      <c r="O59" t="s">
+        <v>325</v>
+      </c>
+      <c r="P59" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>35</v>
+      </c>
+      <c r="R59" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="60" spans="13:18">
+      <c r="M60" t="s">
+        <v>17</v>
+      </c>
+      <c r="N60" t="s">
+        <v>326</v>
+      </c>
+      <c r="O60" t="s">
+        <v>327</v>
+      </c>
+      <c r="P60" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>35</v>
+      </c>
+      <c r="R60" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="61" spans="13:18">
+      <c r="M61" t="s">
+        <v>17</v>
+      </c>
+      <c r="N61" t="s">
+        <v>328</v>
+      </c>
+      <c r="O61" t="s">
+        <v>329</v>
+      </c>
+      <c r="P61" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>35</v>
+      </c>
+      <c r="R61" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="62" spans="13:18">
+      <c r="M62" t="s">
+        <v>17</v>
+      </c>
+      <c r="N62" t="s">
+        <v>330</v>
+      </c>
+      <c r="O62" t="s">
+        <v>331</v>
+      </c>
+      <c r="P62" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>35</v>
+      </c>
+      <c r="R62" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="63" spans="13:18">
+      <c r="M63" t="s">
+        <v>17</v>
+      </c>
+      <c r="N63" t="s">
+        <v>332</v>
+      </c>
+      <c r="O63" t="s">
+        <v>333</v>
+      </c>
+      <c r="P63" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>35</v>
+      </c>
+      <c r="R63" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="64" spans="13:18">
+      <c r="M64" t="s">
+        <v>17</v>
+      </c>
+      <c r="N64" t="s">
+        <v>334</v>
+      </c>
+      <c r="O64" t="s">
+        <v>335</v>
+      </c>
+      <c r="P64" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>35</v>
+      </c>
+      <c r="R64" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="65" spans="13:18">
+      <c r="M65" t="s">
+        <v>17</v>
+      </c>
+      <c r="N65" t="s">
+        <v>336</v>
+      </c>
+      <c r="O65" t="s">
+        <v>337</v>
+      </c>
+      <c r="P65" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>35</v>
+      </c>
+      <c r="R65" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="66" spans="13:18">
+      <c r="M66" t="s">
+        <v>17</v>
+      </c>
+      <c r="N66" t="s">
+        <v>338</v>
+      </c>
+      <c r="O66" t="s">
+        <v>339</v>
+      </c>
+      <c r="P66" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>35</v>
+      </c>
+      <c r="R66" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="67" spans="13:18">
+      <c r="M67" t="s">
+        <v>17</v>
+      </c>
+      <c r="N67" t="s">
+        <v>340</v>
+      </c>
+      <c r="O67" t="s">
+        <v>341</v>
+      </c>
+      <c r="P67" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q67" t="s">
+        <v>35</v>
+      </c>
+      <c r="R67" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="68" spans="13:18">
+      <c r="M68" t="s">
+        <v>17</v>
+      </c>
+      <c r="N68" t="s">
+        <v>342</v>
+      </c>
+      <c r="O68" t="s">
+        <v>343</v>
+      </c>
+      <c r="P68" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q68" t="s">
+        <v>35</v>
+      </c>
+      <c r="R68" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="69" spans="13:18">
+      <c r="M69" t="s">
+        <v>17</v>
+      </c>
+      <c r="N69" t="s">
+        <v>344</v>
+      </c>
+      <c r="O69" t="s">
+        <v>345</v>
+      </c>
+      <c r="P69" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>35</v>
+      </c>
+      <c r="R69" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="70" spans="13:18">
+      <c r="M70" t="s">
+        <v>17</v>
+      </c>
+      <c r="N70" t="s">
+        <v>346</v>
+      </c>
+      <c r="O70" t="s">
+        <v>347</v>
+      </c>
+      <c r="P70" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q70" t="s">
+        <v>35</v>
+      </c>
+      <c r="R70" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="71" spans="13:18">
+      <c r="M71" t="s">
+        <v>17</v>
+      </c>
+      <c r="N71" t="s">
+        <v>348</v>
+      </c>
+      <c r="O71" t="s">
+        <v>349</v>
+      </c>
+      <c r="P71" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q71" t="s">
+        <v>35</v>
+      </c>
+      <c r="R71" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="72" spans="13:18">
+      <c r="M72" t="s">
+        <v>17</v>
+      </c>
+      <c r="N72" t="s">
+        <v>350</v>
+      </c>
+      <c r="O72" t="s">
+        <v>351</v>
+      </c>
+      <c r="P72" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>35</v>
+      </c>
+      <c r="R72" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="73" spans="13:18">
+      <c r="M73" t="s">
+        <v>17</v>
+      </c>
+      <c r="N73" t="s">
+        <v>352</v>
+      </c>
+      <c r="O73" t="s">
+        <v>353</v>
+      </c>
+      <c r="P73" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>35</v>
+      </c>
+      <c r="R73" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="74" spans="13:18">
+      <c r="M74" t="s">
+        <v>17</v>
+      </c>
+      <c r="N74" t="s">
+        <v>354</v>
+      </c>
+      <c r="O74" t="s">
+        <v>355</v>
+      </c>
+      <c r="P74" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q74" t="s">
+        <v>35</v>
+      </c>
+      <c r="R74" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="75" spans="13:18">
+      <c r="M75" t="s">
+        <v>17</v>
+      </c>
+      <c r="N75" t="s">
+        <v>356</v>
+      </c>
+      <c r="O75" t="s">
+        <v>357</v>
+      </c>
+      <c r="P75" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>35</v>
+      </c>
+      <c r="R75" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="76" spans="13:18">
+      <c r="M76" t="s">
+        <v>17</v>
+      </c>
+      <c r="N76" t="s">
+        <v>358</v>
+      </c>
+      <c r="O76" t="s">
+        <v>359</v>
+      </c>
+      <c r="P76" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q76" t="s">
+        <v>35</v>
+      </c>
+      <c r="R76" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="77" spans="13:18">
+      <c r="M77" t="s">
+        <v>17</v>
+      </c>
+      <c r="N77" t="s">
+        <v>360</v>
+      </c>
+      <c r="O77" t="s">
+        <v>361</v>
+      </c>
+      <c r="P77" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q77" t="s">
+        <v>35</v>
+      </c>
+      <c r="R77" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="78" spans="13:18">
+      <c r="M78" t="s">
+        <v>17</v>
+      </c>
+      <c r="N78" t="s">
+        <v>362</v>
+      </c>
+      <c r="O78" t="s">
+        <v>363</v>
+      </c>
+      <c r="P78" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q78" t="s">
+        <v>35</v>
+      </c>
+      <c r="R78" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="79" spans="13:18">
+      <c r="M79" t="s">
+        <v>17</v>
+      </c>
+      <c r="N79" t="s">
+        <v>364</v>
+      </c>
+      <c r="O79" t="s">
+        <v>365</v>
+      </c>
+      <c r="P79" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q79" t="s">
+        <v>35</v>
+      </c>
+      <c r="R79" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="80" spans="13:18">
+      <c r="M80" t="s">
+        <v>17</v>
+      </c>
+      <c r="N80" t="s">
+        <v>366</v>
+      </c>
+      <c r="O80" t="s">
+        <v>367</v>
+      </c>
+      <c r="P80" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q80" t="s">
+        <v>35</v>
+      </c>
+      <c r="R80" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="81" spans="13:18">
+      <c r="M81" t="s">
+        <v>17</v>
+      </c>
+      <c r="N81" t="s">
+        <v>368</v>
+      </c>
+      <c r="O81" t="s">
+        <v>369</v>
+      </c>
+      <c r="P81" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q81" t="s">
+        <v>35</v>
+      </c>
+      <c r="R81" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="82" spans="13:18">
+      <c r="M82" t="s">
+        <v>17</v>
+      </c>
+      <c r="N82" t="s">
+        <v>370</v>
+      </c>
+      <c r="O82" t="s">
+        <v>371</v>
+      </c>
+      <c r="P82" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q82" t="s">
+        <v>35</v>
+      </c>
+      <c r="R82" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="83" spans="13:18">
+      <c r="M83" t="s">
+        <v>17</v>
+      </c>
+      <c r="N83" t="s">
+        <v>372</v>
+      </c>
+      <c r="O83" t="s">
+        <v>373</v>
+      </c>
+      <c r="P83" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q83" t="s">
+        <v>35</v>
+      </c>
+      <c r="R83" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="84" spans="13:18">
+      <c r="M84" t="s">
+        <v>17</v>
+      </c>
+      <c r="N84" t="s">
+        <v>374</v>
+      </c>
+      <c r="O84" t="s">
+        <v>375</v>
+      </c>
+      <c r="P84" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q84" t="s">
+        <v>35</v>
+      </c>
+      <c r="R84" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="85" spans="13:18">
+      <c r="M85" t="s">
+        <v>17</v>
+      </c>
+      <c r="N85" t="s">
+        <v>376</v>
+      </c>
+      <c r="O85" t="s">
+        <v>377</v>
+      </c>
+      <c r="P85" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q85" t="s">
+        <v>35</v>
+      </c>
+      <c r="R85" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="86" spans="13:18">
+      <c r="M86" t="s">
+        <v>17</v>
+      </c>
+      <c r="N86" t="s">
+        <v>378</v>
+      </c>
+      <c r="O86" t="s">
+        <v>379</v>
+      </c>
+      <c r="P86" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q86" t="s">
+        <v>35</v>
+      </c>
+      <c r="R86" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="87" spans="13:18">
+      <c r="M87" t="s">
+        <v>17</v>
+      </c>
+      <c r="N87" t="s">
+        <v>380</v>
+      </c>
+      <c r="O87" t="s">
+        <v>381</v>
+      </c>
+      <c r="P87" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q87" t="s">
+        <v>35</v>
+      </c>
+      <c r="R87" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="88" spans="13:18">
+      <c r="M88" t="s">
+        <v>17</v>
+      </c>
+      <c r="N88" t="s">
+        <v>382</v>
+      </c>
+      <c r="O88" t="s">
+        <v>383</v>
+      </c>
+      <c r="P88" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q88" t="s">
+        <v>35</v>
+      </c>
+      <c r="R88" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="89" spans="13:18">
+      <c r="M89" t="s">
+        <v>17</v>
+      </c>
+      <c r="N89" t="s">
+        <v>384</v>
+      </c>
+      <c r="O89" t="s">
+        <v>385</v>
+      </c>
+      <c r="P89" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q89" t="s">
+        <v>35</v>
+      </c>
+      <c r="R89" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="90" spans="13:18">
+      <c r="M90" t="s">
+        <v>17</v>
+      </c>
+      <c r="N90" t="s">
+        <v>386</v>
+      </c>
+      <c r="O90" t="s">
+        <v>387</v>
+      </c>
+      <c r="P90" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q90" t="s">
+        <v>35</v>
+      </c>
+      <c r="R90" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="91" spans="13:18">
+      <c r="M91" t="s">
+        <v>17</v>
+      </c>
+      <c r="N91" t="s">
+        <v>388</v>
+      </c>
+      <c r="O91" t="s">
+        <v>389</v>
+      </c>
+      <c r="P91" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q91" t="s">
+        <v>35</v>
+      </c>
+      <c r="R91" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="92" spans="13:18">
+      <c r="M92" t="s">
+        <v>17</v>
+      </c>
+      <c r="N92" t="s">
+        <v>390</v>
+      </c>
+      <c r="O92" t="s">
+        <v>391</v>
+      </c>
+      <c r="P92" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q92" t="s">
+        <v>35</v>
+      </c>
+      <c r="R92" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="93" spans="13:18">
+      <c r="M93" t="s">
+        <v>17</v>
+      </c>
+      <c r="N93" t="s">
+        <v>392</v>
+      </c>
+      <c r="O93" t="s">
+        <v>393</v>
+      </c>
+      <c r="P93" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q93" t="s">
+        <v>35</v>
+      </c>
+      <c r="R93" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="94" spans="13:18">
+      <c r="M94" t="s">
+        <v>17</v>
+      </c>
+      <c r="N94" t="s">
+        <v>394</v>
+      </c>
+      <c r="O94" t="s">
+        <v>395</v>
+      </c>
+      <c r="P94" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q94" t="s">
+        <v>35</v>
+      </c>
+      <c r="R94" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="95" spans="13:18">
+      <c r="M95" t="s">
+        <v>17</v>
+      </c>
+      <c r="N95" t="s">
+        <v>396</v>
+      </c>
+      <c r="O95" t="s">
+        <v>397</v>
+      </c>
+      <c r="P95" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q95" t="s">
+        <v>35</v>
+      </c>
+      <c r="R95" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="96" spans="13:18">
+      <c r="M96" t="s">
+        <v>17</v>
+      </c>
+      <c r="N96" t="s">
+        <v>398</v>
+      </c>
+      <c r="O96" t="s">
+        <v>399</v>
+      </c>
+      <c r="P96" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q96" t="s">
+        <v>35</v>
+      </c>
+      <c r="R96" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="97" spans="13:18">
+      <c r="M97" t="s">
+        <v>17</v>
+      </c>
+      <c r="N97" t="s">
+        <v>400</v>
+      </c>
+      <c r="O97" t="s">
+        <v>401</v>
+      </c>
+      <c r="P97" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q97" t="s">
+        <v>35</v>
+      </c>
+      <c r="R97" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="98" spans="13:18">
+      <c r="M98" t="s">
+        <v>17</v>
+      </c>
+      <c r="N98" t="s">
+        <v>402</v>
+      </c>
+      <c r="O98" t="s">
+        <v>403</v>
+      </c>
+      <c r="P98" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q98" t="s">
+        <v>35</v>
+      </c>
+      <c r="R98" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="99" spans="13:18">
+      <c r="M99" t="s">
+        <v>17</v>
+      </c>
+      <c r="N99" t="s">
+        <v>404</v>
+      </c>
+      <c r="O99" t="s">
+        <v>405</v>
+      </c>
+      <c r="P99" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q99" t="s">
+        <v>35</v>
+      </c>
+      <c r="R99" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="100" spans="13:18">
+      <c r="M100" t="s">
+        <v>17</v>
+      </c>
+      <c r="N100" t="s">
+        <v>406</v>
+      </c>
+      <c r="O100" t="s">
+        <v>407</v>
+      </c>
+      <c r="P100" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q100" t="s">
+        <v>35</v>
+      </c>
+      <c r="R100" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="101" spans="13:18">
+      <c r="M101" t="s">
+        <v>17</v>
+      </c>
+      <c r="N101" t="s">
+        <v>408</v>
+      </c>
+      <c r="O101" t="s">
+        <v>409</v>
+      </c>
+      <c r="P101" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q101" t="s">
+        <v>35</v>
+      </c>
+      <c r="R101" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="102" spans="13:18">
+      <c r="M102" t="s">
+        <v>17</v>
+      </c>
+      <c r="N102" t="s">
+        <v>410</v>
+      </c>
+      <c r="O102" t="s">
+        <v>411</v>
+      </c>
+      <c r="P102" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q102" t="s">
+        <v>35</v>
+      </c>
+      <c r="R102" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="103" spans="13:18">
+      <c r="M103" t="s">
+        <v>17</v>
+      </c>
+      <c r="N103" t="s">
+        <v>412</v>
+      </c>
+      <c r="O103" t="s">
+        <v>413</v>
+      </c>
+      <c r="P103" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q103" t="s">
+        <v>35</v>
+      </c>
+      <c r="R103" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="104" spans="13:18">
+      <c r="M104" t="s">
+        <v>17</v>
+      </c>
+      <c r="N104" t="s">
+        <v>414</v>
+      </c>
+      <c r="O104" t="s">
+        <v>415</v>
+      </c>
+      <c r="P104" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q104" t="s">
+        <v>35</v>
+      </c>
+      <c r="R104" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="105" spans="13:18">
+      <c r="M105" t="s">
+        <v>17</v>
+      </c>
+      <c r="N105" t="s">
+        <v>416</v>
+      </c>
+      <c r="O105" t="s">
+        <v>417</v>
+      </c>
+      <c r="P105" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q105" t="s">
+        <v>35</v>
+      </c>
+      <c r="R105" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="106" spans="13:18">
+      <c r="M106" t="s">
+        <v>17</v>
+      </c>
+      <c r="N106" t="s">
+        <v>418</v>
+      </c>
+      <c r="O106" t="s">
+        <v>419</v>
+      </c>
+      <c r="P106" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q106" t="s">
+        <v>35</v>
+      </c>
+      <c r="R106" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="107" spans="13:18">
+      <c r="M107" t="s">
+        <v>17</v>
+      </c>
+      <c r="N107" t="s">
+        <v>420</v>
+      </c>
+      <c r="O107" t="s">
+        <v>421</v>
+      </c>
+      <c r="P107" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q107" t="s">
+        <v>35</v>
+      </c>
+      <c r="R107" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="108" spans="13:18">
+      <c r="M108" t="s">
+        <v>17</v>
+      </c>
+      <c r="N108" t="s">
+        <v>422</v>
+      </c>
+      <c r="O108" t="s">
+        <v>423</v>
+      </c>
+      <c r="P108" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q108" t="s">
+        <v>35</v>
+      </c>
+      <c r="R108" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="109" spans="13:18">
+      <c r="M109" t="s">
+        <v>17</v>
+      </c>
+      <c r="N109" t="s">
+        <v>424</v>
+      </c>
+      <c r="O109" t="s">
+        <v>425</v>
+      </c>
+      <c r="P109" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q109" t="s">
+        <v>35</v>
+      </c>
+      <c r="R109" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="110" spans="13:18">
+      <c r="M110" t="s">
+        <v>17</v>
+      </c>
+      <c r="N110" t="s">
+        <v>426</v>
+      </c>
+      <c r="O110" t="s">
+        <v>427</v>
+      </c>
+      <c r="P110" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q110" t="s">
+        <v>35</v>
+      </c>
+      <c r="R110" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="111" spans="13:18">
+      <c r="M111" t="s">
+        <v>17</v>
+      </c>
+      <c r="N111" t="s">
+        <v>428</v>
+      </c>
+      <c r="O111" t="s">
+        <v>429</v>
+      </c>
+      <c r="P111" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q111" t="s">
+        <v>35</v>
+      </c>
+      <c r="R111" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="112" spans="13:18">
+      <c r="M112" t="s">
+        <v>17</v>
+      </c>
+      <c r="N112" t="s">
+        <v>430</v>
+      </c>
+      <c r="O112" t="s">
+        <v>431</v>
+      </c>
+      <c r="P112" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q112" t="s">
+        <v>35</v>
+      </c>
+      <c r="R112" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="113" spans="13:18">
+      <c r="M113" t="s">
+        <v>17</v>
+      </c>
+      <c r="N113" t="s">
+        <v>432</v>
+      </c>
+      <c r="O113" t="s">
+        <v>433</v>
+      </c>
+      <c r="P113" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q113" t="s">
+        <v>35</v>
+      </c>
+      <c r="R113" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="114" spans="13:18">
+      <c r="M114" t="s">
+        <v>17</v>
+      </c>
+      <c r="N114" t="s">
+        <v>434</v>
+      </c>
+      <c r="O114" t="s">
+        <v>435</v>
+      </c>
+      <c r="P114" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q114" t="s">
+        <v>35</v>
+      </c>
+      <c r="R114" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="115" spans="13:18">
+      <c r="M115" t="s">
+        <v>17</v>
+      </c>
+      <c r="N115" t="s">
+        <v>436</v>
+      </c>
+      <c r="O115" t="s">
+        <v>437</v>
+      </c>
+      <c r="P115" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q115" t="s">
+        <v>35</v>
+      </c>
+      <c r="R115" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="116" spans="13:18">
+      <c r="M116" t="s">
+        <v>17</v>
+      </c>
+      <c r="N116" t="s">
+        <v>438</v>
+      </c>
+      <c r="O116" t="s">
+        <v>439</v>
+      </c>
+      <c r="P116" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q116" t="s">
+        <v>35</v>
+      </c>
+      <c r="R116" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="117" spans="13:18">
+      <c r="M117" t="s">
+        <v>17</v>
+      </c>
+      <c r="N117" t="s">
+        <v>440</v>
+      </c>
+      <c r="O117" t="s">
+        <v>441</v>
+      </c>
+      <c r="P117" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q117" t="s">
+        <v>35</v>
+      </c>
+      <c r="R117" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="118" spans="13:18">
+      <c r="M118" t="s">
+        <v>17</v>
+      </c>
+      <c r="N118" t="s">
+        <v>442</v>
+      </c>
+      <c r="O118" t="s">
+        <v>443</v>
+      </c>
+      <c r="P118" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q118" t="s">
+        <v>35</v>
+      </c>
+      <c r="R118" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="119" spans="13:18">
+      <c r="M119" t="s">
+        <v>17</v>
+      </c>
+      <c r="N119" t="s">
+        <v>444</v>
+      </c>
+      <c r="O119" t="s">
+        <v>445</v>
+      </c>
+      <c r="P119" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q119" t="s">
+        <v>35</v>
+      </c>
+      <c r="R119" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="120" spans="13:18">
+      <c r="M120" t="s">
+        <v>17</v>
+      </c>
+      <c r="N120" t="s">
+        <v>446</v>
+      </c>
+      <c r="O120" t="s">
+        <v>447</v>
+      </c>
+      <c r="P120" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q120" t="s">
+        <v>35</v>
+      </c>
+      <c r="R120" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="121" spans="13:18">
+      <c r="M121" t="s">
+        <v>17</v>
+      </c>
+      <c r="N121" t="s">
+        <v>448</v>
+      </c>
+      <c r="O121" t="s">
+        <v>449</v>
+      </c>
+      <c r="P121" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q121" t="s">
+        <v>35</v>
+      </c>
+      <c r="R121" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="122" spans="13:18">
+      <c r="M122" t="s">
+        <v>17</v>
+      </c>
+      <c r="N122" t="s">
+        <v>450</v>
+      </c>
+      <c r="O122" t="s">
+        <v>451</v>
+      </c>
+      <c r="P122" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q122" t="s">
+        <v>35</v>
+      </c>
+      <c r="R122" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="123" spans="13:18">
+      <c r="M123" t="s">
+        <v>17</v>
+      </c>
+      <c r="N123" t="s">
+        <v>452</v>
+      </c>
+      <c r="O123" t="s">
+        <v>453</v>
+      </c>
+      <c r="P123" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q123" t="s">
+        <v>35</v>
+      </c>
+      <c r="R123" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="124" spans="13:18">
+      <c r="M124" t="s">
+        <v>17</v>
+      </c>
+      <c r="N124" t="s">
+        <v>454</v>
+      </c>
+      <c r="O124" t="s">
+        <v>455</v>
+      </c>
+      <c r="P124" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q124" t="s">
+        <v>35</v>
+      </c>
+      <c r="R124" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="125" spans="13:18">
+      <c r="M125" t="s">
+        <v>17</v>
+      </c>
+      <c r="N125" t="s">
+        <v>456</v>
+      </c>
+      <c r="O125" t="s">
+        <v>457</v>
+      </c>
+      <c r="P125" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q125" t="s">
+        <v>35</v>
+      </c>
+      <c r="R125" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="126" spans="13:18">
+      <c r="M126" t="s">
+        <v>17</v>
+      </c>
+      <c r="N126" t="s">
+        <v>458</v>
+      </c>
+      <c r="O126" t="s">
+        <v>459</v>
+      </c>
+      <c r="P126" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q126" t="s">
+        <v>35</v>
+      </c>
+      <c r="R126" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="127" spans="13:18">
+      <c r="M127" t="s">
+        <v>17</v>
+      </c>
+      <c r="N127" t="s">
+        <v>460</v>
+      </c>
+      <c r="O127" t="s">
+        <v>461</v>
+      </c>
+      <c r="P127" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q127" t="s">
+        <v>35</v>
+      </c>
+      <c r="R127" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="128" spans="13:18">
+      <c r="M128" t="s">
+        <v>17</v>
+      </c>
+      <c r="N128" t="s">
+        <v>462</v>
+      </c>
+      <c r="O128" t="s">
+        <v>463</v>
+      </c>
+      <c r="P128" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q128" t="s">
+        <v>35</v>
+      </c>
+      <c r="R128" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="129" spans="13:18">
+      <c r="M129" t="s">
+        <v>17</v>
+      </c>
+      <c r="N129" t="s">
+        <v>464</v>
+      </c>
+      <c r="O129" t="s">
+        <v>465</v>
+      </c>
+      <c r="P129" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q129" t="s">
+        <v>35</v>
+      </c>
+      <c r="R129" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="130" spans="13:18">
+      <c r="M130" t="s">
+        <v>17</v>
+      </c>
+      <c r="N130" t="s">
+        <v>466</v>
+      </c>
+      <c r="O130" t="s">
+        <v>467</v>
+      </c>
+      <c r="P130" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q130" t="s">
+        <v>35</v>
+      </c>
+      <c r="R130" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="131" spans="13:18">
+      <c r="M131" t="s">
+        <v>17</v>
+      </c>
+      <c r="N131" t="s">
+        <v>468</v>
+      </c>
+      <c r="O131" t="s">
+        <v>469</v>
+      </c>
+      <c r="P131" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q131" t="s">
+        <v>35</v>
+      </c>
+      <c r="R131" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="132" spans="13:18">
+      <c r="M132" t="s">
+        <v>17</v>
+      </c>
+      <c r="N132" t="s">
+        <v>470</v>
+      </c>
+      <c r="O132" t="s">
+        <v>471</v>
+      </c>
+      <c r="P132" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q132" t="s">
+        <v>35</v>
+      </c>
+      <c r="R132" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="133" spans="13:18">
+      <c r="M133" t="s">
+        <v>17</v>
+      </c>
+      <c r="N133" t="s">
+        <v>472</v>
+      </c>
+      <c r="O133" t="s">
+        <v>473</v>
+      </c>
+      <c r="P133" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q133" t="s">
+        <v>35</v>
+      </c>
+      <c r="R133" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="134" spans="13:18">
+      <c r="M134" t="s">
+        <v>17</v>
+      </c>
+      <c r="N134" t="s">
+        <v>474</v>
+      </c>
+      <c r="O134" t="s">
+        <v>475</v>
+      </c>
+      <c r="P134" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q134" t="s">
+        <v>35</v>
+      </c>
+      <c r="R134" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="135" spans="13:18">
+      <c r="M135" t="s">
+        <v>17</v>
+      </c>
+      <c r="N135" t="s">
+        <v>476</v>
+      </c>
+      <c r="O135" t="s">
+        <v>477</v>
+      </c>
+      <c r="P135" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q135" t="s">
+        <v>35</v>
+      </c>
+      <c r="R135" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="136" spans="13:18">
+      <c r="M136" t="s">
+        <v>17</v>
+      </c>
+      <c r="N136" t="s">
+        <v>478</v>
+      </c>
+      <c r="O136" t="s">
+        <v>479</v>
+      </c>
+      <c r="P136" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q136" t="s">
+        <v>35</v>
+      </c>
+      <c r="R136" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="137" spans="13:18">
+      <c r="M137" t="s">
+        <v>17</v>
+      </c>
+      <c r="N137" t="s">
+        <v>480</v>
+      </c>
+      <c r="O137" t="s">
+        <v>481</v>
+      </c>
+      <c r="P137" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q137" t="s">
+        <v>35</v>
+      </c>
+      <c r="R137" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="138" spans="13:18">
+      <c r="M138" t="s">
+        <v>17</v>
+      </c>
+      <c r="N138" t="s">
+        <v>482</v>
+      </c>
+      <c r="O138" t="s">
+        <v>483</v>
+      </c>
+      <c r="P138" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q138" t="s">
+        <v>35</v>
+      </c>
+      <c r="R138" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="139" spans="13:18">
+      <c r="M139" t="s">
+        <v>17</v>
+      </c>
+      <c r="N139" t="s">
+        <v>484</v>
+      </c>
+      <c r="O139" t="s">
+        <v>485</v>
+      </c>
+      <c r="P139" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q139" t="s">
+        <v>35</v>
+      </c>
+      <c r="R139" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="140" spans="13:18">
+      <c r="M140" t="s">
+        <v>17</v>
+      </c>
+      <c r="N140" t="s">
+        <v>486</v>
+      </c>
+      <c r="O140" t="s">
+        <v>487</v>
+      </c>
+      <c r="P140" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q140" t="s">
+        <v>35</v>
+      </c>
+      <c r="R140" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="141" spans="13:18">
+      <c r="M141" t="s">
+        <v>17</v>
+      </c>
+      <c r="N141" t="s">
+        <v>488</v>
+      </c>
+      <c r="O141" t="s">
+        <v>489</v>
+      </c>
+      <c r="P141" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q141" t="s">
+        <v>35</v>
+      </c>
+      <c r="R141" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="142" spans="13:18">
+      <c r="M142" t="s">
+        <v>17</v>
+      </c>
+      <c r="N142" t="s">
+        <v>490</v>
+      </c>
+      <c r="O142" t="s">
+        <v>491</v>
+      </c>
+      <c r="P142" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q142" t="s">
+        <v>35</v>
+      </c>
+      <c r="R142" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="143" spans="13:18">
+      <c r="M143" t="s">
+        <v>17</v>
+      </c>
+      <c r="N143" t="s">
+        <v>492</v>
+      </c>
+      <c r="O143" t="s">
+        <v>493</v>
+      </c>
+      <c r="P143" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q143" t="s">
+        <v>35</v>
+      </c>
+      <c r="R143" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="144" spans="13:18">
+      <c r="M144" t="s">
+        <v>17</v>
+      </c>
+      <c r="N144" t="s">
+        <v>494</v>
+      </c>
+      <c r="O144" t="s">
+        <v>495</v>
+      </c>
+      <c r="P144" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q144" t="s">
+        <v>35</v>
+      </c>
+      <c r="R144" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="145" spans="13:18">
+      <c r="M145" t="s">
+        <v>17</v>
+      </c>
+      <c r="N145" t="s">
+        <v>496</v>
+      </c>
+      <c r="O145" t="s">
+        <v>497</v>
+      </c>
+      <c r="P145" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q145" t="s">
+        <v>35</v>
+      </c>
+      <c r="R145" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="146" spans="13:18">
+      <c r="M146" t="s">
+        <v>17</v>
+      </c>
+      <c r="N146" t="s">
+        <v>498</v>
+      </c>
+      <c r="O146" t="s">
+        <v>499</v>
+      </c>
+      <c r="P146" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q146" t="s">
+        <v>35</v>
+      </c>
+      <c r="R146" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="147" spans="13:18">
+      <c r="M147" t="s">
+        <v>17</v>
+      </c>
+      <c r="N147" t="s">
+        <v>500</v>
+      </c>
+      <c r="O147" t="s">
+        <v>501</v>
+      </c>
+      <c r="P147" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q147" t="s">
+        <v>35</v>
+      </c>
+      <c r="R147" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="148" spans="13:18">
+      <c r="M148" t="s">
+        <v>17</v>
+      </c>
+      <c r="N148" t="s">
+        <v>502</v>
+      </c>
+      <c r="O148" t="s">
+        <v>503</v>
+      </c>
+      <c r="P148" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q148" t="s">
+        <v>35</v>
+      </c>
+      <c r="R148" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="149" spans="13:18">
+      <c r="M149" t="s">
+        <v>17</v>
+      </c>
+      <c r="N149" t="s">
+        <v>504</v>
+      </c>
+      <c r="O149" t="s">
+        <v>505</v>
+      </c>
+      <c r="P149" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q149" t="s">
+        <v>35</v>
+      </c>
+      <c r="R149" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="150" spans="13:18">
+      <c r="M150" t="s">
+        <v>17</v>
+      </c>
+      <c r="N150" t="s">
+        <v>506</v>
+      </c>
+      <c r="O150" t="s">
+        <v>507</v>
+      </c>
+      <c r="P150" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q150" t="s">
+        <v>35</v>
+      </c>
+      <c r="R150" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="151" spans="13:18">
+      <c r="M151" t="s">
+        <v>17</v>
+      </c>
+      <c r="N151" t="s">
+        <v>508</v>
+      </c>
+      <c r="O151" t="s">
+        <v>509</v>
+      </c>
+      <c r="P151" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q151" t="s">
+        <v>35</v>
+      </c>
+      <c r="R151" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="152" spans="13:18">
+      <c r="M152" t="s">
+        <v>17</v>
+      </c>
+      <c r="N152" t="s">
+        <v>510</v>
+      </c>
+      <c r="O152" t="s">
+        <v>511</v>
+      </c>
+      <c r="P152" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q152" t="s">
+        <v>35</v>
+      </c>
+      <c r="R152" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="153" spans="13:18">
+      <c r="M153" t="s">
+        <v>17</v>
+      </c>
+      <c r="N153" t="s">
+        <v>512</v>
+      </c>
+      <c r="O153" t="s">
+        <v>513</v>
+      </c>
+      <c r="P153" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q153" t="s">
+        <v>35</v>
+      </c>
+      <c r="R153" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="154" spans="13:18">
+      <c r="M154" t="s">
+        <v>17</v>
+      </c>
+      <c r="N154" t="s">
+        <v>514</v>
+      </c>
+      <c r="O154" t="s">
+        <v>515</v>
+      </c>
+      <c r="P154" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q154" t="s">
+        <v>35</v>
+      </c>
+      <c r="R154" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="155" spans="13:18">
+      <c r="M155" t="s">
+        <v>17</v>
+      </c>
+      <c r="N155" t="s">
+        <v>516</v>
+      </c>
+      <c r="O155" t="s">
+        <v>517</v>
+      </c>
+      <c r="P155" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q155" t="s">
+        <v>35</v>
+      </c>
+      <c r="R155" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="156" spans="13:18">
+      <c r="M156" t="s">
+        <v>17</v>
+      </c>
+      <c r="N156" t="s">
+        <v>518</v>
+      </c>
+      <c r="O156" t="s">
+        <v>519</v>
+      </c>
+      <c r="P156" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q156" t="s">
+        <v>35</v>
+      </c>
+      <c r="R156" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="157" spans="13:18">
+      <c r="M157" t="s">
+        <v>17</v>
+      </c>
+      <c r="N157" t="s">
+        <v>520</v>
+      </c>
+      <c r="O157" t="s">
+        <v>521</v>
+      </c>
+      <c r="P157" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q157" t="s">
+        <v>35</v>
+      </c>
+      <c r="R157" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="158" spans="13:18">
+      <c r="M158" t="s">
+        <v>17</v>
+      </c>
+      <c r="N158" t="s">
+        <v>522</v>
+      </c>
+      <c r="O158" t="s">
+        <v>523</v>
+      </c>
+      <c r="P158" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q158" t="s">
+        <v>35</v>
+      </c>
+      <c r="R158" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="159" spans="13:18">
+      <c r="M159" t="s">
+        <v>17</v>
+      </c>
+      <c r="N159" t="s">
+        <v>524</v>
+      </c>
+      <c r="O159" t="s">
+        <v>525</v>
+      </c>
+      <c r="P159" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q159" t="s">
+        <v>35</v>
+      </c>
+      <c r="R159" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="160" spans="13:18">
+      <c r="M160" t="s">
+        <v>17</v>
+      </c>
+      <c r="N160" t="s">
+        <v>526</v>
+      </c>
+      <c r="O160" t="s">
+        <v>527</v>
+      </c>
+      <c r="P160" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q160" t="s">
+        <v>35</v>
+      </c>
+      <c r="R160" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="161" spans="13:18">
+      <c r="M161" t="s">
+        <v>17</v>
+      </c>
+      <c r="N161" t="s">
+        <v>528</v>
+      </c>
+      <c r="O161" t="s">
+        <v>529</v>
+      </c>
+      <c r="P161" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q161" t="s">
+        <v>35</v>
+      </c>
+      <c r="R161" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="162" spans="13:18">
+      <c r="M162" t="s">
+        <v>17</v>
+      </c>
+      <c r="N162" t="s">
+        <v>530</v>
+      </c>
+      <c r="O162" t="s">
+        <v>531</v>
+      </c>
+      <c r="P162" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q162" t="s">
+        <v>35</v>
+      </c>
+      <c r="R162" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="163" spans="13:18">
+      <c r="M163" t="s">
+        <v>17</v>
+      </c>
+      <c r="N163" t="s">
+        <v>532</v>
+      </c>
+      <c r="O163" t="s">
+        <v>533</v>
+      </c>
+      <c r="P163" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q163" t="s">
+        <v>35</v>
+      </c>
+      <c r="R163" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="164" spans="13:18">
+      <c r="M164" t="s">
+        <v>17</v>
+      </c>
+      <c r="N164" t="s">
+        <v>534</v>
+      </c>
+      <c r="O164" t="s">
+        <v>535</v>
+      </c>
+      <c r="P164" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q164" t="s">
+        <v>35</v>
+      </c>
+      <c r="R164" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="165" spans="13:18">
+      <c r="M165" t="s">
+        <v>17</v>
+      </c>
+      <c r="N165" t="s">
+        <v>536</v>
+      </c>
+      <c r="O165" t="s">
+        <v>537</v>
+      </c>
+      <c r="P165" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q165" t="s">
+        <v>35</v>
+      </c>
+      <c r="R165" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="166" spans="13:18">
+      <c r="M166" t="s">
+        <v>17</v>
+      </c>
+      <c r="N166" t="s">
+        <v>538</v>
+      </c>
+      <c r="O166" t="s">
+        <v>539</v>
+      </c>
+      <c r="P166" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q166" t="s">
+        <v>35</v>
+      </c>
+      <c r="R166" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="167" spans="13:18">
+      <c r="M167" t="s">
+        <v>17</v>
+      </c>
+      <c r="N167" t="s">
+        <v>540</v>
+      </c>
+      <c r="O167" t="s">
+        <v>541</v>
+      </c>
+      <c r="P167" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q167" t="s">
+        <v>35</v>
+      </c>
+      <c r="R167" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="168" spans="13:18">
+      <c r="M168" t="s">
+        <v>17</v>
+      </c>
+      <c r="N168" t="s">
+        <v>542</v>
+      </c>
+      <c r="O168" t="s">
+        <v>543</v>
+      </c>
+      <c r="P168" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q168" t="s">
+        <v>35</v>
+      </c>
+      <c r="R168" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="169" spans="13:18">
+      <c r="M169" t="s">
+        <v>17</v>
+      </c>
+      <c r="N169" t="s">
+        <v>544</v>
+      </c>
+      <c r="O169" t="s">
+        <v>545</v>
+      </c>
+      <c r="P169" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q169" t="s">
+        <v>35</v>
+      </c>
+      <c r="R169" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="170" spans="13:18">
+      <c r="M170" t="s">
+        <v>17</v>
+      </c>
+      <c r="N170" t="s">
+        <v>546</v>
+      </c>
+      <c r="O170" t="s">
+        <v>547</v>
+      </c>
+      <c r="P170" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q170" t="s">
+        <v>35</v>
+      </c>
+      <c r="R170" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="171" spans="13:18">
+      <c r="M171" t="s">
+        <v>17</v>
+      </c>
+      <c r="N171" t="s">
+        <v>548</v>
+      </c>
+      <c r="O171" t="s">
+        <v>549</v>
+      </c>
+      <c r="P171" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q171" t="s">
+        <v>35</v>
+      </c>
+      <c r="R171" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="172" spans="13:18">
+      <c r="M172" t="s">
+        <v>17</v>
+      </c>
+      <c r="N172" t="s">
+        <v>550</v>
+      </c>
+      <c r="O172" t="s">
+        <v>551</v>
+      </c>
+      <c r="P172" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q172" t="s">
+        <v>35</v>
+      </c>
+      <c r="R172" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="173" spans="13:18">
+      <c r="M173" t="s">
+        <v>17</v>
+      </c>
+      <c r="N173" t="s">
+        <v>552</v>
+      </c>
+      <c r="O173" t="s">
+        <v>553</v>
+      </c>
+      <c r="P173" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q173" t="s">
+        <v>35</v>
+      </c>
+      <c r="R173" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="174" spans="13:18">
+      <c r="M174" t="s">
+        <v>17</v>
+      </c>
+      <c r="N174" t="s">
+        <v>554</v>
+      </c>
+      <c r="O174" t="s">
+        <v>555</v>
+      </c>
+      <c r="P174" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q174" t="s">
+        <v>35</v>
+      </c>
+      <c r="R174" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="175" spans="13:18">
+      <c r="M175" t="s">
+        <v>17</v>
+      </c>
+      <c r="N175" t="s">
+        <v>556</v>
+      </c>
+      <c r="O175" t="s">
+        <v>557</v>
+      </c>
+      <c r="P175" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q175" t="s">
+        <v>35</v>
+      </c>
+      <c r="R175" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="176" spans="13:18">
+      <c r="M176" t="s">
+        <v>17</v>
+      </c>
+      <c r="N176" t="s">
+        <v>558</v>
+      </c>
+      <c r="O176" t="s">
+        <v>559</v>
+      </c>
+      <c r="P176" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q176" t="s">
+        <v>35</v>
+      </c>
+      <c r="R176" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="177" spans="13:18">
+      <c r="M177" t="s">
+        <v>17</v>
+      </c>
+      <c r="N177" t="s">
+        <v>560</v>
+      </c>
+      <c r="O177" t="s">
+        <v>561</v>
+      </c>
+      <c r="P177" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q177" t="s">
+        <v>35</v>
+      </c>
+      <c r="R177" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="178" spans="13:18">
+      <c r="M178" t="s">
+        <v>17</v>
+      </c>
+      <c r="N178" t="s">
+        <v>562</v>
+      </c>
+      <c r="O178" t="s">
+        <v>563</v>
+      </c>
+      <c r="P178" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q178" t="s">
+        <v>35</v>
+      </c>
+      <c r="R178" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="179" spans="13:18">
+      <c r="M179" t="s">
+        <v>17</v>
+      </c>
+      <c r="N179" t="s">
+        <v>564</v>
+      </c>
+      <c r="O179" t="s">
+        <v>565</v>
+      </c>
+      <c r="P179" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q179" t="s">
+        <v>35</v>
+      </c>
+      <c r="R179" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="180" spans="13:18">
+      <c r="M180" t="s">
+        <v>17</v>
+      </c>
+      <c r="N180" t="s">
+        <v>566</v>
+      </c>
+      <c r="O180" t="s">
+        <v>567</v>
+      </c>
+      <c r="P180" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q180" t="s">
+        <v>35</v>
+      </c>
+      <c r="R180" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="181" spans="13:18">
+      <c r="M181" t="s">
+        <v>17</v>
+      </c>
+      <c r="N181" t="s">
+        <v>568</v>
+      </c>
+      <c r="O181" t="s">
+        <v>569</v>
+      </c>
+      <c r="P181" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q181" t="s">
+        <v>35</v>
+      </c>
+      <c r="R181" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="182" spans="13:18">
+      <c r="M182" t="s">
+        <v>17</v>
+      </c>
+      <c r="N182" t="s">
+        <v>570</v>
+      </c>
+      <c r="O182" t="s">
+        <v>571</v>
+      </c>
+      <c r="P182" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q182" t="s">
+        <v>35</v>
+      </c>
+      <c r="R182" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="183" spans="13:18">
+      <c r="M183" t="s">
+        <v>17</v>
+      </c>
+      <c r="N183" t="s">
+        <v>572</v>
+      </c>
+      <c r="O183" t="s">
+        <v>573</v>
+      </c>
+      <c r="P183" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q183" t="s">
+        <v>35</v>
+      </c>
+      <c r="R183" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="184" spans="13:18">
+      <c r="M184" t="s">
+        <v>17</v>
+      </c>
+      <c r="N184" t="s">
+        <v>574</v>
+      </c>
+      <c r="O184" t="s">
+        <v>575</v>
+      </c>
+      <c r="P184" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q184" t="s">
+        <v>35</v>
+      </c>
+      <c r="R184" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="185" spans="13:18">
+      <c r="M185" t="s">
+        <v>17</v>
+      </c>
+      <c r="N185" t="s">
+        <v>576</v>
+      </c>
+      <c r="O185" t="s">
+        <v>577</v>
+      </c>
+      <c r="P185" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q185" t="s">
+        <v>35</v>
+      </c>
+      <c r="R185" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="186" spans="13:18">
+      <c r="M186" t="s">
+        <v>17</v>
+      </c>
+      <c r="N186" t="s">
+        <v>578</v>
+      </c>
+      <c r="O186" t="s">
+        <v>579</v>
+      </c>
+      <c r="P186" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q186" t="s">
+        <v>35</v>
+      </c>
+      <c r="R186" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="187" spans="13:18">
+      <c r="M187" t="s">
+        <v>17</v>
+      </c>
+      <c r="N187" t="s">
+        <v>580</v>
+      </c>
+      <c r="O187" t="s">
+        <v>581</v>
+      </c>
+      <c r="P187" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q187" t="s">
+        <v>35</v>
+      </c>
+      <c r="R187" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="188" spans="13:18">
+      <c r="M188" t="s">
+        <v>17</v>
+      </c>
+      <c r="N188" t="s">
+        <v>582</v>
+      </c>
+      <c r="O188" t="s">
+        <v>583</v>
+      </c>
+      <c r="P188" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q188" t="s">
+        <v>35</v>
+      </c>
+      <c r="R188" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="189" spans="13:18">
+      <c r="M189" t="s">
+        <v>17</v>
+      </c>
+      <c r="N189" t="s">
+        <v>584</v>
+      </c>
+      <c r="O189" t="s">
+        <v>585</v>
+      </c>
+      <c r="P189" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q189" t="s">
+        <v>35</v>
+      </c>
+      <c r="R189" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="190" spans="13:18">
+      <c r="M190" t="s">
+        <v>17</v>
+      </c>
+      <c r="N190" t="s">
+        <v>586</v>
+      </c>
+      <c r="O190" t="s">
+        <v>587</v>
+      </c>
+      <c r="P190" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q190" t="s">
+        <v>35</v>
+      </c>
+      <c r="R190" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="191" spans="13:18">
+      <c r="M191" t="s">
+        <v>17</v>
+      </c>
+      <c r="N191" t="s">
+        <v>588</v>
+      </c>
+      <c r="O191" t="s">
+        <v>589</v>
+      </c>
+      <c r="P191" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q191" t="s">
+        <v>35</v>
+      </c>
+      <c r="R191" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="192" spans="13:18">
+      <c r="M192" t="s">
+        <v>17</v>
+      </c>
+      <c r="N192" t="s">
+        <v>590</v>
+      </c>
+      <c r="O192" t="s">
+        <v>591</v>
+      </c>
+      <c r="P192" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q192" t="s">
+        <v>35</v>
+      </c>
+      <c r="R192" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="193" spans="13:18">
+      <c r="M193" t="s">
+        <v>17</v>
+      </c>
+      <c r="N193" t="s">
+        <v>592</v>
+      </c>
+      <c r="O193" t="s">
+        <v>593</v>
+      </c>
+      <c r="P193" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q193" t="s">
+        <v>35</v>
+      </c>
+      <c r="R193" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="194" spans="13:18">
+      <c r="M194" t="s">
+        <v>17</v>
+      </c>
+      <c r="N194" t="s">
+        <v>594</v>
+      </c>
+      <c r="O194" t="s">
+        <v>595</v>
+      </c>
+      <c r="P194" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q194" t="s">
+        <v>35</v>
+      </c>
+      <c r="R194" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="195" spans="13:18">
+      <c r="M195" t="s">
+        <v>17</v>
+      </c>
+      <c r="N195" t="s">
+        <v>596</v>
+      </c>
+      <c r="O195" t="s">
+        <v>597</v>
+      </c>
+      <c r="P195" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q195" t="s">
+        <v>35</v>
+      </c>
+      <c r="R195" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="196" spans="13:18">
+      <c r="M196" t="s">
+        <v>17</v>
+      </c>
+      <c r="N196" t="s">
+        <v>598</v>
+      </c>
+      <c r="O196" t="s">
+        <v>599</v>
+      </c>
+      <c r="P196" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q196" t="s">
+        <v>35</v>
+      </c>
+      <c r="R196" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="197" spans="13:18">
+      <c r="M197" t="s">
+        <v>17</v>
+      </c>
+      <c r="N197" t="s">
+        <v>600</v>
+      </c>
+      <c r="O197" t="s">
+        <v>601</v>
+      </c>
+      <c r="P197" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q197" t="s">
+        <v>35</v>
+      </c>
+      <c r="R197" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="198" spans="13:18">
+      <c r="M198" t="s">
+        <v>17</v>
+      </c>
+      <c r="N198" t="s">
+        <v>602</v>
+      </c>
+      <c r="O198" t="s">
+        <v>603</v>
+      </c>
+      <c r="P198" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q198" t="s">
+        <v>35</v>
+      </c>
+      <c r="R198" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="199" spans="13:18">
+      <c r="M199" t="s">
+        <v>17</v>
+      </c>
+      <c r="N199" t="s">
+        <v>604</v>
+      </c>
+      <c r="O199" t="s">
+        <v>605</v>
+      </c>
+      <c r="P199" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q199" t="s">
+        <v>35</v>
+      </c>
+      <c r="R199" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="200" spans="13:18">
+      <c r="M200" t="s">
+        <v>17</v>
+      </c>
+      <c r="N200" t="s">
+        <v>606</v>
+      </c>
+      <c r="O200" t="s">
+        <v>607</v>
+      </c>
+      <c r="P200" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q200" t="s">
+        <v>35</v>
+      </c>
+      <c r="R200" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="201" spans="13:18">
+      <c r="M201" t="s">
+        <v>17</v>
+      </c>
+      <c r="N201" t="s">
+        <v>608</v>
+      </c>
+      <c r="O201" t="s">
+        <v>609</v>
+      </c>
+      <c r="P201" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q201" t="s">
+        <v>35</v>
+      </c>
+      <c r="R201" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="202" spans="13:18">
+      <c r="M202" t="s">
+        <v>17</v>
+      </c>
+      <c r="N202" t="s">
+        <v>610</v>
+      </c>
+      <c r="O202" t="s">
+        <v>611</v>
+      </c>
+      <c r="P202" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q202" t="s">
+        <v>35</v>
+      </c>
+      <c r="R202" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="203" spans="13:18">
+      <c r="M203" t="s">
+        <v>17</v>
+      </c>
+      <c r="N203" t="s">
+        <v>612</v>
+      </c>
+      <c r="O203" t="s">
+        <v>613</v>
+      </c>
+      <c r="P203" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q203" t="s">
+        <v>35</v>
+      </c>
+      <c r="R203" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="204" spans="13:18">
+      <c r="M204" t="s">
+        <v>17</v>
+      </c>
+      <c r="N204" t="s">
+        <v>614</v>
+      </c>
+      <c r="O204" t="s">
+        <v>615</v>
+      </c>
+      <c r="P204" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q204" t="s">
+        <v>35</v>
+      </c>
+      <c r="R204" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="205" spans="13:18">
+      <c r="M205" t="s">
+        <v>17</v>
+      </c>
+      <c r="N205" t="s">
+        <v>616</v>
+      </c>
+      <c r="O205" t="s">
+        <v>617</v>
+      </c>
+      <c r="P205" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q205" t="s">
+        <v>35</v>
+      </c>
+      <c r="R205" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="206" spans="13:18">
+      <c r="M206" t="s">
+        <v>17</v>
+      </c>
+      <c r="N206" t="s">
+        <v>618</v>
+      </c>
+      <c r="O206" t="s">
+        <v>619</v>
+      </c>
+      <c r="P206" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q206" t="s">
+        <v>35</v>
+      </c>
+      <c r="R206" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="207" spans="13:18">
+      <c r="M207" t="s">
+        <v>17</v>
+      </c>
+      <c r="N207" t="s">
+        <v>620</v>
+      </c>
+      <c r="O207" t="s">
+        <v>621</v>
+      </c>
+      <c r="P207" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q207" t="s">
+        <v>35</v>
+      </c>
+      <c r="R207" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="208" spans="13:18">
+      <c r="M208" t="s">
+        <v>17</v>
+      </c>
+      <c r="N208" t="s">
+        <v>622</v>
+      </c>
+      <c r="O208" t="s">
+        <v>623</v>
+      </c>
+      <c r="P208" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q208" t="s">
+        <v>35</v>
+      </c>
+      <c r="R208" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="209" spans="13:18">
+      <c r="M209" t="s">
+        <v>17</v>
+      </c>
+      <c r="N209" t="s">
+        <v>624</v>
+      </c>
+      <c r="O209" t="s">
+        <v>625</v>
+      </c>
+      <c r="P209" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q209" t="s">
+        <v>35</v>
+      </c>
+      <c r="R209" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="210" spans="13:18">
+      <c r="M210" t="s">
+        <v>17</v>
+      </c>
+      <c r="N210" t="s">
+        <v>626</v>
+      </c>
+      <c r="O210" t="s">
+        <v>627</v>
+      </c>
+      <c r="P210" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q210" t="s">
+        <v>35</v>
+      </c>
+      <c r="R210" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="211" spans="13:18">
+      <c r="M211" t="s">
+        <v>17</v>
+      </c>
+      <c r="N211" t="s">
+        <v>628</v>
+      </c>
+      <c r="O211" t="s">
+        <v>629</v>
+      </c>
+      <c r="P211" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q211" t="s">
+        <v>35</v>
+      </c>
+      <c r="R211" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="212" spans="13:18">
+      <c r="M212" t="s">
+        <v>17</v>
+      </c>
+      <c r="N212" t="s">
+        <v>630</v>
+      </c>
+      <c r="O212" t="s">
+        <v>631</v>
+      </c>
+      <c r="P212" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q212" t="s">
+        <v>35</v>
+      </c>
+      <c r="R212" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="213" spans="13:18">
+      <c r="M213" t="s">
+        <v>17</v>
+      </c>
+      <c r="N213" t="s">
+        <v>632</v>
+      </c>
+      <c r="O213" t="s">
+        <v>633</v>
+      </c>
+      <c r="P213" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q213" t="s">
+        <v>35</v>
+      </c>
+      <c r="R213" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="214" spans="13:18">
+      <c r="M214" t="s">
+        <v>17</v>
+      </c>
+      <c r="N214" t="s">
+        <v>634</v>
+      </c>
+      <c r="O214" t="s">
+        <v>635</v>
+      </c>
+      <c r="P214" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q214" t="s">
+        <v>35</v>
+      </c>
+      <c r="R214" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="215" spans="13:18">
+      <c r="M215" t="s">
+        <v>17</v>
+      </c>
+      <c r="N215" t="s">
+        <v>636</v>
+      </c>
+      <c r="O215" t="s">
+        <v>637</v>
+      </c>
+      <c r="P215" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q215" t="s">
+        <v>35</v>
+      </c>
+      <c r="R215" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="216" spans="13:18">
+      <c r="M216" t="s">
+        <v>17</v>
+      </c>
+      <c r="N216" t="s">
+        <v>638</v>
+      </c>
+      <c r="O216" t="s">
+        <v>639</v>
+      </c>
+      <c r="P216" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q216" t="s">
+        <v>35</v>
+      </c>
+      <c r="R216" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="217" spans="13:18">
+      <c r="M217" t="s">
+        <v>17</v>
+      </c>
+      <c r="N217" t="s">
+        <v>640</v>
+      </c>
+      <c r="O217" t="s">
+        <v>641</v>
+      </c>
+      <c r="P217" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q217" t="s">
+        <v>35</v>
+      </c>
+      <c r="R217" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="218" spans="13:18">
+      <c r="M218" t="s">
+        <v>17</v>
+      </c>
+      <c r="N218" t="s">
+        <v>642</v>
+      </c>
+      <c r="O218" t="s">
+        <v>643</v>
+      </c>
+      <c r="P218" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q218" t="s">
+        <v>35</v>
+      </c>
+      <c r="R218" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="219" spans="13:18">
+      <c r="M219" t="s">
+        <v>17</v>
+      </c>
+      <c r="N219" t="s">
+        <v>644</v>
+      </c>
+      <c r="O219" t="s">
+        <v>645</v>
+      </c>
+      <c r="P219" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q219" t="s">
+        <v>35</v>
+      </c>
+      <c r="R219" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="220" spans="13:18">
+      <c r="M220" t="s">
+        <v>17</v>
+      </c>
+      <c r="N220" t="s">
+        <v>646</v>
+      </c>
+      <c r="O220" t="s">
+        <v>647</v>
+      </c>
+      <c r="P220" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q220" t="s">
+        <v>35</v>
+      </c>
+      <c r="R220" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="221" spans="13:18">
+      <c r="M221" t="s">
+        <v>17</v>
+      </c>
+      <c r="N221" t="s">
+        <v>648</v>
+      </c>
+      <c r="O221" t="s">
+        <v>649</v>
+      </c>
+      <c r="P221" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q221" t="s">
+        <v>35</v>
+      </c>
+      <c r="R221" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="222" spans="13:18">
+      <c r="M222" t="s">
+        <v>17</v>
+      </c>
+      <c r="N222" t="s">
+        <v>650</v>
+      </c>
+      <c r="O222" t="s">
+        <v>651</v>
+      </c>
+      <c r="P222" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q222" t="s">
+        <v>35</v>
+      </c>
+      <c r="R222" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="223" spans="13:18">
+      <c r="M223" t="s">
+        <v>17</v>
+      </c>
+      <c r="N223" t="s">
+        <v>652</v>
+      </c>
+      <c r="O223" t="s">
+        <v>653</v>
+      </c>
+      <c r="P223" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q223" t="s">
+        <v>35</v>
+      </c>
+      <c r="R223" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="224" spans="13:18">
+      <c r="M224" t="s">
+        <v>17</v>
+      </c>
+      <c r="N224" t="s">
+        <v>654</v>
+      </c>
+      <c r="O224" t="s">
+        <v>655</v>
+      </c>
+      <c r="P224" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q224" t="s">
+        <v>35</v>
+      </c>
+      <c r="R224" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="225" spans="13:18">
+      <c r="M225" t="s">
+        <v>17</v>
+      </c>
+      <c r="N225" t="s">
+        <v>656</v>
+      </c>
+      <c r="O225" t="s">
+        <v>657</v>
+      </c>
+      <c r="P225" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q225" t="s">
+        <v>35</v>
+      </c>
+      <c r="R225" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="226" spans="13:18">
+      <c r="M226" t="s">
+        <v>17</v>
+      </c>
+      <c r="N226" t="s">
+        <v>658</v>
+      </c>
+      <c r="O226" t="s">
+        <v>659</v>
+      </c>
+      <c r="P226" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q226" t="s">
+        <v>35</v>
+      </c>
+      <c r="R226" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="227" spans="13:18">
+      <c r="M227" t="s">
+        <v>17</v>
+      </c>
+      <c r="N227" t="s">
+        <v>660</v>
+      </c>
+      <c r="O227" t="s">
+        <v>661</v>
+      </c>
+      <c r="P227" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q227" t="s">
+        <v>35</v>
+      </c>
+      <c r="R227" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="228" spans="13:18">
+      <c r="M228" t="s">
+        <v>17</v>
+      </c>
+      <c r="N228" t="s">
+        <v>662</v>
+      </c>
+      <c r="O228" t="s">
+        <v>663</v>
+      </c>
+      <c r="P228" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q228" t="s">
+        <v>35</v>
+      </c>
+      <c r="R228" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="229" spans="13:18">
+      <c r="M229" t="s">
+        <v>17</v>
+      </c>
+      <c r="N229" t="s">
+        <v>664</v>
+      </c>
+      <c r="O229" t="s">
+        <v>665</v>
+      </c>
+      <c r="P229" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q229" t="s">
+        <v>35</v>
+      </c>
+      <c r="R229" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="230" spans="13:18">
+      <c r="M230" t="s">
+        <v>17</v>
+      </c>
+      <c r="N230" t="s">
+        <v>666</v>
+      </c>
+      <c r="O230" t="s">
+        <v>667</v>
+      </c>
+      <c r="P230" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q230" t="s">
+        <v>35</v>
+      </c>
+      <c r="R230" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="231" spans="13:18">
+      <c r="M231" t="s">
+        <v>17</v>
+      </c>
+      <c r="N231" t="s">
+        <v>668</v>
+      </c>
+      <c r="O231" t="s">
+        <v>669</v>
+      </c>
+      <c r="P231" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q231" t="s">
+        <v>35</v>
+      </c>
+      <c r="R231" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="232" spans="13:18">
+      <c r="M232" t="s">
+        <v>17</v>
+      </c>
+      <c r="N232" t="s">
+        <v>670</v>
+      </c>
+      <c r="O232" t="s">
+        <v>671</v>
+      </c>
+      <c r="P232" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q232" t="s">
+        <v>35</v>
+      </c>
+      <c r="R232" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="233" spans="13:18">
+      <c r="M233" t="s">
+        <v>17</v>
+      </c>
+      <c r="N233" t="s">
+        <v>672</v>
+      </c>
+      <c r="O233" t="s">
+        <v>673</v>
+      </c>
+      <c r="P233" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q233" t="s">
+        <v>35</v>
+      </c>
+      <c r="R233" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="234" spans="13:18">
+      <c r="M234" t="s">
+        <v>17</v>
+      </c>
+      <c r="N234" t="s">
+        <v>674</v>
+      </c>
+      <c r="O234" t="s">
+        <v>675</v>
+      </c>
+      <c r="P234" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q234" t="s">
+        <v>35</v>
+      </c>
+      <c r="R234" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="235" spans="13:18">
+      <c r="M235" t="s">
+        <v>17</v>
+      </c>
+      <c r="N235" t="s">
+        <v>676</v>
+      </c>
+      <c r="O235" t="s">
+        <v>677</v>
+      </c>
+      <c r="P235" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q235" t="s">
+        <v>35</v>
+      </c>
+      <c r="R235" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="236" spans="13:18">
+      <c r="M236" t="s">
+        <v>17</v>
+      </c>
+      <c r="N236" t="s">
+        <v>678</v>
+      </c>
+      <c r="O236" t="s">
+        <v>679</v>
+      </c>
+      <c r="P236" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q236" t="s">
+        <v>35</v>
+      </c>
+      <c r="R236" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="237" spans="13:18">
+      <c r="M237" t="s">
+        <v>17</v>
+      </c>
+      <c r="N237" t="s">
+        <v>680</v>
+      </c>
+      <c r="O237" t="s">
+        <v>681</v>
+      </c>
+      <c r="P237" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q237" t="s">
+        <v>35</v>
+      </c>
+      <c r="R237" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="238" spans="13:18">
+      <c r="M238" t="s">
+        <v>17</v>
+      </c>
+      <c r="N238" t="s">
+        <v>682</v>
+      </c>
+      <c r="O238" t="s">
+        <v>683</v>
+      </c>
+      <c r="P238" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q238" t="s">
+        <v>35</v>
+      </c>
+      <c r="R238" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="239" spans="13:18">
+      <c r="M239" t="s">
+        <v>17</v>
+      </c>
+      <c r="N239" t="s">
+        <v>684</v>
+      </c>
+      <c r="O239" t="s">
+        <v>685</v>
+      </c>
+      <c r="P239" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q239" t="s">
+        <v>35</v>
+      </c>
+      <c r="R239" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="240" spans="13:18">
+      <c r="M240" t="s">
+        <v>17</v>
+      </c>
+      <c r="N240" t="s">
+        <v>686</v>
+      </c>
+      <c r="O240" t="s">
+        <v>687</v>
+      </c>
+      <c r="P240" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q240" t="s">
+        <v>35</v>
+      </c>
+      <c r="R240" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="241" spans="13:18">
+      <c r="M241" t="s">
+        <v>17</v>
+      </c>
+      <c r="N241" t="s">
+        <v>688</v>
+      </c>
+      <c r="O241" t="s">
+        <v>689</v>
+      </c>
+      <c r="P241" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q241" t="s">
+        <v>35</v>
+      </c>
+      <c r="R241" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="242" spans="13:18">
+      <c r="M242" t="s">
+        <v>17</v>
+      </c>
+      <c r="N242" t="s">
+        <v>690</v>
+      </c>
+      <c r="O242" t="s">
+        <v>691</v>
+      </c>
+      <c r="P242" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q242" t="s">
+        <v>35</v>
+      </c>
+      <c r="R242" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="243" spans="13:18">
+      <c r="M243" t="s">
+        <v>17</v>
+      </c>
+      <c r="N243" t="s">
+        <v>692</v>
+      </c>
+      <c r="O243" t="s">
+        <v>693</v>
+      </c>
+      <c r="P243" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q243" t="s">
+        <v>35</v>
+      </c>
+      <c r="R243" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="244" spans="13:18">
+      <c r="M244" t="s">
+        <v>17</v>
+      </c>
+      <c r="N244" t="s">
+        <v>694</v>
+      </c>
+      <c r="O244" t="s">
+        <v>695</v>
+      </c>
+      <c r="P244" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q244" t="s">
+        <v>35</v>
+      </c>
+      <c r="R244" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="245" spans="13:18">
+      <c r="M245" t="s">
+        <v>17</v>
+      </c>
+      <c r="N245" t="s">
+        <v>696</v>
+      </c>
+      <c r="O245" t="s">
+        <v>697</v>
+      </c>
+      <c r="P245" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q245" t="s">
+        <v>35</v>
+      </c>
+      <c r="R245" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="246" spans="13:18">
+      <c r="M246" t="s">
+        <v>17</v>
+      </c>
+      <c r="N246" t="s">
+        <v>698</v>
+      </c>
+      <c r="O246" t="s">
+        <v>699</v>
+      </c>
+      <c r="P246" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q246" t="s">
+        <v>35</v>
+      </c>
+      <c r="R246" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="247" spans="13:18">
+      <c r="M247" t="s">
+        <v>17</v>
+      </c>
+      <c r="N247" t="s">
+        <v>700</v>
+      </c>
+      <c r="O247" t="s">
+        <v>701</v>
+      </c>
+      <c r="P247" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q247" t="s">
+        <v>35</v>
+      </c>
+      <c r="R247" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="248" spans="13:18">
+      <c r="M248" t="s">
+        <v>17</v>
+      </c>
+      <c r="N248" t="s">
+        <v>702</v>
+      </c>
+      <c r="O248" t="s">
+        <v>703</v>
+      </c>
+      <c r="P248" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q248" t="s">
+        <v>35</v>
+      </c>
+      <c r="R248" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="249" spans="13:18">
+      <c r="M249" t="s">
+        <v>17</v>
+      </c>
+      <c r="N249" t="s">
+        <v>704</v>
+      </c>
+      <c r="O249" t="s">
+        <v>705</v>
+      </c>
+      <c r="P249" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q249" t="s">
+        <v>35</v>
+      </c>
+      <c r="R249" t="s">
+        <v>217</v>
       </c>
     </row>
   </sheetData>
@@ -3796,7 +10057,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A64C410-895F-4040-A7AB-3F7211AA7FBD}">
-  <dimension ref="B1:N41"/>
+  <dimension ref="B1:N42"/>
   <sheetFormatPr defaultColWidth="11.3984375" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="11.3984375" style="11"/>
@@ -3938,49 +10199,49 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="2:12">
-      <c r="B13" s="14" t="s">
+    <row r="11" spans="2:12">
+      <c r="D11" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="E11" s="11">
+        <v>0</v>
+      </c>
+      <c r="F11" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12">
+      <c r="B14" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="14"/>
-    </row>
-    <row r="14" spans="2:12">
-      <c r="B14" s="15" t="s">
+      <c r="G14" s="14"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="14"/>
+    </row>
+    <row r="15" spans="2:12">
+      <c r="B15" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="C15" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="D14" s="15" t="s">
+      <c r="D15" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="E14" s="15" t="s">
+      <c r="E15" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="F14" s="15" t="s">
+      <c r="F15" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="G14" s="15" t="s">
+      <c r="G15" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="H14" s="15" t="s">
+      <c r="H15" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="I14" s="15" t="s">
+      <c r="I15" s="15" t="s">
         <v>56</v>
-      </c>
-    </row>
-    <row r="15" spans="2:12">
-      <c r="D15" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="F15" s="11">
-        <v>2222</v>
-      </c>
-      <c r="G15" s="11" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="16" spans="2:12">
@@ -3988,22 +10249,22 @@
         <v>66</v>
       </c>
       <c r="F16" s="11">
+        <v>2222</v>
+      </c>
+      <c r="G16" s="11" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="17" spans="2:14">
+      <c r="D17" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="F17" s="11">
         <v>8888</v>
       </c>
-      <c r="G16" s="11" t="s">
+      <c r="G17" s="11" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="17" spans="2:14" ht="12.75">
-      <c r="B17" s="13"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
-      <c r="I17" s="13"/>
-      <c r="J17" s="13"/>
     </row>
     <row r="18" spans="2:14" ht="12.75">
       <c r="B18" s="13"/>
@@ -4027,20 +10288,16 @@
       <c r="I19" s="13"/>
       <c r="J19" s="13"/>
     </row>
-    <row r="20" spans="2:14" ht="14.25">
-      <c r="B20"/>
-      <c r="C20"/>
-      <c r="D20"/>
-      <c r="E20"/>
-      <c r="F20"/>
-      <c r="G20"/>
-      <c r="H20"/>
-      <c r="I20"/>
-      <c r="J20"/>
-      <c r="K20"/>
-      <c r="L20"/>
-      <c r="M20"/>
-      <c r="N20"/>
+    <row r="20" spans="2:14" ht="12.75">
+      <c r="B20" s="13"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="13"/>
+      <c r="H20" s="13"/>
+      <c r="I20" s="13"/>
+      <c r="J20" s="13"/>
     </row>
     <row r="21" spans="2:14" ht="14.25">
       <c r="B21"/>
@@ -4356,6 +10613,21 @@
       <c r="L41"/>
       <c r="M41"/>
       <c r="N41"/>
+    </row>
+    <row r="42" spans="2:14" ht="14.25">
+      <c r="B42"/>
+      <c r="C42"/>
+      <c r="D42"/>
+      <c r="E42"/>
+      <c r="F42"/>
+      <c r="G42"/>
+      <c r="H42"/>
+      <c r="I42"/>
+      <c r="J42"/>
+      <c r="K42"/>
+      <c r="L42"/>
+      <c r="M42"/>
+      <c r="N42"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
